--- a/MATH/M07/bus123-math-m07-l01-starter.xlsx
+++ b/MATH/M07/bus123-math-m07-l01-starter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/private/tmp/bus123-m07-review/outputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/tmp/bus123-m07-review/ab-outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF853822-A71F-9244-A16B-A66C89700614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A150F5AE-2600-284B-923F-B93A3BC429F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="25600" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="38400" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="START HERE" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="183">
   <si>
     <t>BUS123 - MATH-M07-L01 - Sales, Excise, and Property Taxes</t>
   </si>
@@ -71,15 +71,9 @@
     <t>Live You Try It</t>
   </si>
   <si>
-    <t>Build with new numbers, explain cell references, then compare with the slide reveals. Feedback checks baseline values and required references.</t>
-  </si>
-  <si>
     <t>Class Challenge</t>
   </si>
   <si>
-    <t>In pairs, audit R01-R03 and one of R04-R06. Complete all six and reconcile for homework.</t>
-  </si>
-  <si>
     <t>FormulaReferenceCard</t>
   </si>
   <si>
@@ -92,15 +86,9 @@
     <t>Yellow input cells</t>
   </si>
   <si>
-    <t>Yellow input cells and answer cells are blank for student work.</t>
-  </si>
-  <si>
     <t>Green feedback cells</t>
   </si>
   <si>
-    <t>Feedback checks baseline values and required references; explain your logic and test changing inputs.</t>
-  </si>
-  <si>
     <t>Yellow audit-repair cells</t>
   </si>
   <si>
@@ -110,9 +98,6 @@
     <t>MATH-M07 - Live You Try It | Self-graded Excel pauses</t>
   </si>
   <si>
-    <t>Enter inputs and formulas in H. Feedback checks baseline values and required references. Attempt first, then compare with the slide reveal. Restore inputs after Predict → Change → Explain.</t>
-  </si>
-  <si>
     <t>#</t>
   </si>
   <si>
@@ -152,9 +137,6 @@
     <t>Subtract the discount before tax under the supplied rule.</t>
   </si>
   <si>
-    <t>slide 8</t>
-  </si>
-  <si>
     <t>E: tax rate 5.75%; H: tax owed using row 1 subtotal.</t>
   </si>
   <si>
@@ -191,21 +173,6 @@
     <t>Reference the supplied base and sales-tax rate.</t>
   </si>
   <si>
-    <t>slide 13</t>
-  </si>
-  <si>
-    <t>E: excise rate 4.5%; H: excise tax using the original base in D11.</t>
-  </si>
-  <si>
-    <t>Reference the same original base cell used for sales tax: D11.</t>
-  </si>
-  <si>
-    <t>H: total cost using original base D11 and tax results H11 and H12.</t>
-  </si>
-  <si>
-    <t>Add the original base and both separate tax results.</t>
-  </si>
-  <si>
     <t>Property tax</t>
   </si>
   <si>
@@ -215,9 +182,6 @@
     <t>Reference market value and the supplied assessment rate.</t>
   </si>
   <si>
-    <t>slide 17</t>
-  </si>
-  <si>
     <t>D: town budget 234,500; E: total assessed value 3,450,000; H: rounded rate.</t>
   </si>
   <si>
@@ -227,13 +191,7 @@
     <t>H: annual tax due using row 9 assessed value and row 10 rounded rate.</t>
   </si>
   <si>
-    <t>Reference assessed value H14 and rounded rate H15.</t>
-  </si>
-  <si>
     <t>MATH-M07 - Class Challenge | Tax Compliance Audit</t>
-  </si>
-  <si>
-    <t>In pairs: audit R01-R03, then one of R04-R06. Finish all six for homework before reconciling to the control total. Enter 0 for OK or 1 for ERROR, repair formulas, and compute adjustments.</t>
   </si>
   <si>
     <t>All cases use the supplied training-jurisdiction rules. Blue-gray cells are source data and stay unchanged. Yellow cells are your audit work. Corrected liabilities must be formulas, not typed answers.</t>
@@ -507,6 +465,129 @@
   </si>
   <si>
     <t>Use for lease cash-flow planning; actual obligations depend on lease terms.</t>
+  </si>
+  <si>
+    <t>Slide 6: follow Version A in rows 22-25, then try Version B in rows 31-34. Later slides use tasks 1-11 above. Compare with the slide reveals.</t>
+  </si>
+  <si>
+    <t>In pairs, audit R01-R03 and one of R04-R06. Complete all six and reconcile for homework.</t>
+  </si>
+  <si>
+    <t>Yellow input cells and answer cells are blank for student work.</t>
+  </si>
+  <si>
+    <t>Feedback checks baseline values and required references; explain your logic and test changing inputs.</t>
+  </si>
+  <si>
+    <t>Enter inputs and formulas in H. Feedback checks baseline values and required references. Attempt first, then compare with the slide reveal. Restore inputs after Predict → Change → Explain.</t>
+  </si>
+  <si>
+    <t>slide 8</t>
+  </si>
+  <si>
+    <t>slide 13</t>
+  </si>
+  <si>
+    <t>E: excise rate 4.5%; H: excise tax using the original base in D11.</t>
+  </si>
+  <si>
+    <t>Reference the same original base cell used for sales tax: D11.</t>
+  </si>
+  <si>
+    <t>H: total cost using original base D11 and tax results H11 and H12.</t>
+  </si>
+  <si>
+    <t>Add the original base and both separate tax results.</t>
+  </si>
+  <si>
+    <t>slide 17</t>
+  </si>
+  <si>
+    <t>Reference assessed value H14 and rounded rate H15.</t>
+  </si>
+  <si>
+    <t>Slide 6 - Reverse sales tax - Version A (follow along)</t>
+  </si>
+  <si>
+    <t>Tidal register receipts of $52,000 include 6.5% sales tax. Enter the givens, calculate pre-tax sales and tax held, and explain why they add back to receipts.</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>Receipts</t>
+  </si>
+  <si>
+    <t>Enter tax-inclusive receipts 52,000 in D22.</t>
+  </si>
+  <si>
+    <t>slide 6</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>Tax rate</t>
+  </si>
+  <si>
+    <t>Enter sales-tax rate 6.5% in E23.</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>Pre-tax sales</t>
+  </si>
+  <si>
+    <t>Calculate sales before tax in H24 using the two inputs above.</t>
+  </si>
+  <si>
+    <t>Explain why the divisor includes 1 plus the tax rate.</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>Tax held</t>
+  </si>
+  <si>
+    <t>Calculate tax held in H25 using receipts and your pre-tax sales result.</t>
+  </si>
+  <si>
+    <t>Sales plus tax held must equal receipts.</t>
+  </si>
+  <si>
+    <t>Slide 6 - Reverse sales tax - Version B (try independently)</t>
+  </si>
+  <si>
+    <t>Tidal register receipts of $43,200 include 8% sales tax. Enter the givens, calculate pre-tax sales and tax held, and explain why they add back to receipts.</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>Enter tax-inclusive receipts 43,200 in D31.</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>Enter sales-tax rate 8% in E32.</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>Calculate sales before tax in H33 using the two inputs above.</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>Calculate tax held in H34 using receipts and your pre-tax sales result.</t>
+  </si>
+  <si>
+    <t>In pairs: audit R01-R03, then one of R04-R06. Finish all six for homework before reconciling to the control total. Enter 0 for OK or 1 for ERROR, repair formulas, and compute adjustments.</t>
   </si>
 </sst>
 </file>
@@ -521,7 +602,7 @@
     <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="169" formatCode="0.00%;[Red]\-0.00%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -603,8 +684,19 @@
       <color rgb="FF9C4A2B"/>
       <name val="DM Sans"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1A1F2C"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -693,7 +785,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2EEE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A7C5E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAF8F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF355773"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD966"/>
       </patternFill>
     </fill>
   </fills>
@@ -849,7 +971,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -980,7 +1102,25 @@
     <xf numFmtId="168" fontId="13" fillId="16" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1007,6 +1147,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1018,69 +1225,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1327,14 +1471,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1"/>
@@ -1345,14 +1489,14 @@
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" ht="24" customHeight="1">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
     </row>
     <row r="4" spans="1:6" ht="32">
       <c r="A4" s="1"/>
@@ -1408,7 +1552,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>11</v>
+        <v>142</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1417,10 +1561,10 @@
     <row r="9" spans="1:6" ht="48" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>13</v>
+        <v>143</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -1429,10 +1573,10 @@
     <row r="10" spans="1:6" ht="48">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -1455,22 +1599,22 @@
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1">
-      <c r="A13" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
+      <c r="A13" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
     </row>
     <row r="14" spans="1:6" ht="32">
       <c r="A14" s="1"/>
       <c r="B14" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -1479,10 +1623,10 @@
     <row r="15" spans="1:6" ht="48">
       <c r="A15" s="1"/>
       <c r="B15" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -1491,10 +1635,10 @@
     <row r="16" spans="1:6" ht="38" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1512,7 +1656,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1525,19 +1669,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="34" customHeight="1">
-      <c r="A1" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
+      <c r="A1" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1"/>
@@ -1553,19 +1697,19 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="42" customHeight="1">
-      <c r="A3" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
+      <c r="A3" s="57" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1"/>
@@ -1582,37 +1726,37 @@
     </row>
     <row r="5" spans="1:11" ht="16">
       <c r="A5" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="32">
@@ -1620,10 +1764,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -1635,10 +1779,10 @@
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="32">
@@ -1646,10 +1790,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="8"/>
@@ -1661,10 +1805,10 @@
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="32">
@@ -1672,10 +1816,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="6"/>
@@ -1687,10 +1831,10 @@
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="16">
@@ -1698,10 +1842,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="8"/>
@@ -1713,10 +1857,10 @@
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="16">
@@ -1724,10 +1868,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -1739,10 +1883,10 @@
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="32">
@@ -1750,10 +1894,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="8"/>
@@ -1765,10 +1909,10 @@
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>51</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="32">
@@ -1776,12 +1920,12 @@
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="44"/>
+        <v>149</v>
+      </c>
+      <c r="D12" s="50"/>
       <c r="E12" s="8"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
@@ -1791,10 +1935,10 @@
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>51</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="32">
@@ -1802,12 +1946,12 @@
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="44"/>
+        <v>151</v>
+      </c>
+      <c r="D13" s="50"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
@@ -1817,10 +1961,10 @@
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>55</v>
+        <v>152</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>51</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="32">
@@ -1828,10 +1972,10 @@
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="8"/>
@@ -1843,10 +1987,10 @@
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>59</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="32">
@@ -1854,10 +1998,10 @@
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -1869,10 +2013,10 @@
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>59</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="32">
@@ -1880,10 +2024,10 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -1895,16 +2039,338 @@
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>63</v>
+        <v>154</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>59</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="30" customHeight="1">
+      <c r="A19" s="59" t="s">
+        <v>155</v>
+      </c>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="59"/>
+    </row>
+    <row r="20" spans="1:11" ht="36" customHeight="1">
+      <c r="A20" s="60" t="s">
+        <v>156</v>
+      </c>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="60"/>
+    </row>
+    <row r="21" spans="1:11" ht="28" customHeight="1">
+      <c r="A21" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="K21" s="47" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="42" customHeight="1">
+      <c r="A22" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" s="44" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22" s="48"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="42" customHeight="1">
+      <c r="A23" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="B23" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="C23" s="44" t="s">
+        <v>163</v>
+      </c>
+      <c r="D23" s="45"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="42" customHeight="1">
+      <c r="A24" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="46" t="str">
+        <f ca="1">IF(COUNT(D22,E23,H24)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(H24)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D22",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(H24)),"$",""))),ISNUMBER(SEARCH("E23",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(H24)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(H24-48826.2910798122)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
+        <v>Enter inputs and a formula first</v>
+      </c>
+      <c r="J24" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="K24" s="44" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="42" customHeight="1">
+      <c r="A25" s="44" t="s">
+        <v>168</v>
+      </c>
+      <c r="B25" s="44" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" s="44" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="46" t="str">
+        <f ca="1">IF(COUNT(D22,H24,H25)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(H25)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D22",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(H25)),"$",""))),ISNUMBER(SEARCH("H24",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(H25)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(H25-3173.70892018778)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
+        <v>Enter inputs and a formula first</v>
+      </c>
+      <c r="J25" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="K25" s="44" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="30" customHeight="1">
+      <c r="A28" s="59" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" s="59"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="59"/>
+      <c r="K28" s="59"/>
+    </row>
+    <row r="29" spans="1:11" ht="36" customHeight="1">
+      <c r="A29" s="60" t="s">
+        <v>173</v>
+      </c>
+      <c r="B29" s="60"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="60"/>
+      <c r="K29" s="60"/>
+    </row>
+    <row r="30" spans="1:11" ht="28" customHeight="1">
+      <c r="A30" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="H30" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="J30" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="K30" s="47" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="42" customHeight="1">
+      <c r="A31" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="B31" s="44" t="s">
+        <v>158</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="D31" s="48"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="44"/>
+      <c r="K31" s="44" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="42" customHeight="1">
+      <c r="A32" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="B32" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="D32" s="45"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="46"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="42" customHeight="1">
+      <c r="A33" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="B33" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="46" t="str">
+        <f ca="1">IF(COUNT(D31,E32,H33)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(H33)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D31",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(H33)),"$",""))),ISNUMBER(SEARCH("E32",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(H33)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(H33-40000)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
+        <v>Enter inputs and a formula first</v>
+      </c>
+      <c r="J33" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="K33" s="44" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="42" customHeight="1">
+      <c r="A34" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" s="44" t="s">
+        <v>169</v>
+      </c>
+      <c r="C34" s="44" t="s">
+        <v>181</v>
+      </c>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="45"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="46" t="str">
+        <f ca="1">IF(COUNT(D31,H33,H34)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(H34)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D31",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(H34)),"$",""))),ISNUMBER(SEARCH("H33",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(H34)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(H34-3200)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
+        <v>Enter inputs and a formula first</v>
+      </c>
+      <c r="J34" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="K34" s="44" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="6">
+    <mergeCell ref="A29:K29"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A28:K28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1930,20 +2396,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="36" customHeight="1">
-      <c r="A1" s="62" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
+      <c r="A1" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="11"/>
@@ -1960,102 +2426,102 @@
       <c r="L2" s="11"/>
     </row>
     <row r="3" spans="1:12" ht="42" customHeight="1">
-      <c r="A3" s="63" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
+      <c r="A3" s="67" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
     </row>
     <row r="4" spans="1:12" ht="32" customHeight="1">
-      <c r="A4" s="64" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
+      <c r="A4" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="65" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68" t="s">
-        <v>68</v>
-      </c>
-      <c r="K5" s="69"/>
-      <c r="L5" s="70"/>
+      <c r="A5" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="72" t="s">
+        <v>54</v>
+      </c>
+      <c r="K5" s="73"/>
+      <c r="L5" s="74"/>
     </row>
     <row r="6" spans="1:12" ht="42" customHeight="1">
       <c r="A6" s="15" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="42" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D7" s="30">
         <v>1200</v>
@@ -2068,7 +2534,7 @@
       </c>
       <c r="G7" s="39"/>
       <c r="H7" s="27" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="I7" s="30">
         <f>ROUND((D7-E7)*F7,2)</f>
@@ -2080,13 +2546,13 @@
     </row>
     <row r="8" spans="1:12" ht="42" customHeight="1">
       <c r="A8" s="20" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D8" s="31">
         <v>480</v>
@@ -2099,7 +2565,7 @@
       </c>
       <c r="G8" s="40"/>
       <c r="H8" s="28" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="I8" s="31">
         <f>ROUND(D8*F8,2)</f>
@@ -2111,13 +2577,13 @@
     </row>
     <row r="9" spans="1:12" ht="42" customHeight="1">
       <c r="A9" s="20" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D9" s="31">
         <v>78625</v>
@@ -2128,7 +2594,7 @@
       </c>
       <c r="G9" s="40"/>
       <c r="H9" s="28" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="I9" s="31">
         <f>ROUND(D9-D9/(1+F9),2)</f>
@@ -2140,13 +2606,13 @@
     </row>
     <row r="10" spans="1:12" ht="42" customHeight="1">
       <c r="A10" s="20" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D10" s="31">
         <v>6200</v>
@@ -2159,7 +2625,7 @@
         <v>0.08</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I10" s="31">
         <f>ROUND(D10*(F10+G10),2)</f>
@@ -2171,13 +2637,13 @@
     </row>
     <row r="11" spans="1:12" ht="42" customHeight="1">
       <c r="A11" s="20" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D11" s="31">
         <v>8400</v>
@@ -2190,7 +2656,7 @@
         <v>0.09</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I11" s="31">
         <f>ROUND(D11*F11+(D11+D11*F11)*G11,2)</f>
@@ -2202,13 +2668,13 @@
     </row>
     <row r="12" spans="1:12" ht="42" customHeight="1">
       <c r="A12" s="22" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D12" s="32">
         <v>820000</v>
@@ -2223,7 +2689,7 @@
         <v>4750000</v>
       </c>
       <c r="H12" s="29" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I12" s="32">
         <f>ROUND(D12*ROUND(F12/G12,4),2)</f>
@@ -2262,43 +2728,43 @@
       <c r="L14" s="11"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="71" t="s">
-        <v>99</v>
-      </c>
-      <c r="B15" s="72"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="72"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="72"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="73"/>
+      <c r="A15" s="75" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="76"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="76"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="76"/>
+      <c r="K15" s="76"/>
+      <c r="L15" s="77"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
+      <c r="A16" s="82" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
       <c r="D16" s="30">
         <f>SUM(I7:I12)</f>
         <v>60590.47</v>
       </c>
-      <c r="E16" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
+      <c r="E16" s="83" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
       <c r="H16" s="30">
         <v>28405.15</v>
       </c>
-      <c r="I16" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="J16" s="55"/>
+      <c r="I16" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="J16" s="84"/>
       <c r="K16" s="34"/>
       <c r="L16" s="11"/>
     </row>
@@ -2311,10 +2777,10 @@
       <c r="F17" s="42"/>
       <c r="G17" s="42"/>
       <c r="H17" s="42"/>
-      <c r="I17" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="J17" s="56"/>
+      <c r="I17" s="85" t="s">
+        <v>89</v>
+      </c>
+      <c r="J17" s="85"/>
       <c r="K17" s="36"/>
       <c r="L17" s="11"/>
     </row>
@@ -2327,10 +2793,10 @@
       <c r="F18" s="42"/>
       <c r="G18" s="42"/>
       <c r="H18" s="42"/>
-      <c r="I18" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="J18" s="56"/>
+      <c r="I18" s="85" t="s">
+        <v>90</v>
+      </c>
+      <c r="J18" s="85"/>
       <c r="K18" s="36"/>
       <c r="L18" s="11"/>
     </row>
@@ -2343,10 +2809,10 @@
       <c r="F19" s="14"/>
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
-      <c r="I19" s="57" t="s">
-        <v>105</v>
-      </c>
-      <c r="J19" s="57"/>
+      <c r="I19" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J19" s="61"/>
       <c r="K19" s="43"/>
       <c r="L19" s="11"/>
     </row>
@@ -2365,34 +2831,34 @@
       <c r="L20" s="11"/>
     </row>
     <row r="21" spans="1:12" ht="32" customHeight="1">
-      <c r="A21" s="58" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" s="59"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="74"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="74"/>
-      <c r="J21" s="74"/>
-      <c r="K21" s="74"/>
-      <c r="L21" s="75"/>
+      <c r="A21" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" s="63"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="78"/>
+      <c r="K21" s="78"/>
+      <c r="L21" s="79"/>
     </row>
     <row r="22" spans="1:12" ht="32" customHeight="1">
-      <c r="A22" s="60"/>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="76"/>
-      <c r="E22" s="76"/>
-      <c r="F22" s="76"/>
-      <c r="G22" s="76"/>
-      <c r="H22" s="76"/>
-      <c r="I22" s="76"/>
-      <c r="J22" s="76"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="77"/>
+      <c r="A22" s="64"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="80"/>
+      <c r="J22" s="80"/>
+      <c r="K22" s="80"/>
+      <c r="L22" s="81"/>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="11"/>
@@ -2460,12 +2926,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
-      <c r="A1" s="49" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
+      <c r="A1" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1"/>
@@ -2475,170 +2941,170 @@
     </row>
     <row r="3" spans="1:4" ht="16">
       <c r="A3" s="4" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="32">
       <c r="A4" s="3" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="32">
       <c r="A5" s="3" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16">
       <c r="A6" s="3" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16">
       <c r="A7" s="3" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16">
       <c r="A8" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="32">
       <c r="A9" s="3" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="32">
       <c r="A10" s="3" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="32">
       <c r="A11" s="3" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="32">
       <c r="A12" s="3" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16">
       <c r="A13" s="3" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="32">
       <c r="A14" s="3" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/MATH/M07/bus123-math-m07-l01-starter.xlsx
+++ b/MATH/M07/bus123-math-m07-l01-starter.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rbc84900cf9054903" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R9f9e8985cc7644c2" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="Rc7640b5273534013" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R403bb12d34f743da" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R1ad4885203454615" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Rd653915775984c40" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R58c4eb960d8d46b1" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R5c99636da0584474" state="visible"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -530,7 +530,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="39">
+  <x:fills count="46">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -615,6 +615,41 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF9C4A2B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2EEE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4A7C5E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFAF8F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF355773"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFD966"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -875,7 +910,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="122">
+  <x:cellXfs count="139">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -1232,6 +1267,55 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="14" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="40" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="40" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="14" fillId="40" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="14" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="14" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="40" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1545,7 +1629,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="3" t="str">
-        <v>Start with slide 6: Version A in rows 8-11, then Version B in rows 17-20. Continue downward: sales tax on slide 8 (rows 24-28), two taxes on slide 13 (rows 29-31), and property tax on slide 17 (rows 32-34).</v>
+        <v>Start with slide 7: Version A in rows 8-11, then Version B in rows 17-20. Continue downward: sales tax on slide 9 (rows 24-28), two taxes on slide 14 (rows 29-31), and property tax on slide 18 (rows 32-34).</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1711,299 +1795,299 @@
       <c r="I4" s="1"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="114" t="str">
-        <v>Slide 6 - Reverse sales tax - Version A (follow along)</v>
-      </c>
-      <c r="B5" s="114"/>
-      <c r="C5" s="114"/>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="114"/>
+      <c r="A5" s="132" t="str">
+        <v>Slide 7 - Reverse sales tax - Version A (follow along)</v>
+      </c>
+      <c r="B5" s="132"/>
+      <c r="C5" s="132"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132"/>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="115" t="str">
+      <c r="A6" s="133" t="str">
         <v>Tidal register receipts of $52,000 include 6.5% sales tax. Enter the givens, calculate pre-tax sales and tax held, and explain why they add back to receipts.</v>
       </c>
-      <c r="B6" s="115"/>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="115"/>
+      <c r="B6" s="133"/>
+      <c r="C6" s="133"/>
+      <c r="D6" s="133"/>
+      <c r="E6" s="133"/>
+      <c r="F6" s="133"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="133"/>
+      <c r="I6" s="133"/>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="116" t="s">
+      <c r="A7" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="116" t="s">
+      <c r="B7" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="116" t="s">
+      <c r="C7" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="116" t="s">
+      <c r="D7" s="134" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="116" t="s">
+      <c r="E7" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="116" t="s">
+      <c r="F7" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="116" t="s">
+      <c r="G7" s="134" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="116" t="s">
+      <c r="H7" s="134" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="116" t="s">
+      <c r="I7" s="134" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="107" t="str">
+      <c r="A8" s="125" t="str">
         <v>A1</v>
       </c>
-      <c r="B8" s="107" t="str">
+      <c r="B8" s="125" t="str">
         <v>Receipts</v>
       </c>
-      <c r="C8" s="107" t="str">
+      <c r="C8" s="125" t="str">
         <v>Enter tax-inclusive receipts 52,000 in D8.</v>
       </c>
-      <c r="D8" s="118"/>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="107"/>
-      <c r="I8" s="107" t="str">
-        <v>slide 6</v>
+      <c r="D8" s="136"/>
+      <c r="E8" s="128"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="131"/>
+      <c r="H8" s="125"/>
+      <c r="I8" s="125" t="str">
+        <v>slide 7</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="107" t="str">
+      <c r="A9" s="125" t="str">
         <v>A2</v>
       </c>
-      <c r="B9" s="107" t="str">
+      <c r="B9" s="125" t="str">
         <v>Tax rate</v>
       </c>
-      <c r="C9" s="107" t="str">
+      <c r="C9" s="125" t="str">
         <v>Enter sales-tax rate 6.5% in E9.</v>
       </c>
-      <c r="D9" s="111"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="113"/>
-      <c r="H9" s="107"/>
-      <c r="I9" s="107" t="str">
-        <v>slide 6</v>
+      <c r="D9" s="129"/>
+      <c r="E9" s="137"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="125" t="str">
+        <v>slide 7</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="107" t="str">
+      <c r="A10" s="125" t="str">
         <v>A3</v>
       </c>
-      <c r="B10" s="107" t="str">
+      <c r="B10" s="125" t="str">
         <v>Pre-tax sales</v>
       </c>
-      <c r="C10" s="107" t="str">
+      <c r="C10" s="125" t="str">
         <v>Calculate sales before tax in F10 using the two inputs above.</v>
       </c>
-      <c r="D10" s="110"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="118"/>
-      <c r="G10" s="113" t="str">
+      <c r="D10" s="128"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="136"/>
+      <c r="G10" s="131" t="str">
         <f>IF(COUNT(D8,E9,F10)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F10)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D8",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F10)),"$",""))),ISNUMBER(SEARCH("E9",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F10)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F10-48826.29107981221)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H10" s="107" t="str">
+      <c r="H10" s="125" t="str">
         <v>Explain why the divisor includes 1 plus the tax rate.</v>
       </c>
-      <c r="I10" s="107" t="str">
-        <v>slide 6</v>
+      <c r="I10" s="125" t="str">
+        <v>slide 7</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="107" t="str">
+      <c r="A11" s="125" t="str">
         <v>A4</v>
       </c>
-      <c r="B11" s="107" t="str">
+      <c r="B11" s="125" t="str">
         <v>Tax held</v>
       </c>
-      <c r="C11" s="107" t="str">
+      <c r="C11" s="125" t="str">
         <v>Calculate tax held in F11 using receipts and your pre-tax sales result.</v>
       </c>
-      <c r="D11" s="110"/>
-      <c r="E11" s="112"/>
-      <c r="F11" s="118"/>
-      <c r="G11" s="113" t="str">
+      <c r="D11" s="128"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="136"/>
+      <c r="G11" s="131" t="str">
         <f>IF(COUNT(D8,F10,F11)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F11)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D8",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F11)),"$",""))),ISNUMBER(SEARCH("F10",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F11)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F11-3173.7089201877898)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H11" s="107" t="str">
+      <c r="H11" s="125" t="str">
         <v>Sales plus tax held must equal receipts.</v>
       </c>
-      <c r="I11" s="107" t="str">
-        <v>slide 6</v>
+      <c r="I11" s="125" t="str">
+        <v>slide 7</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="114" t="str">
-        <v>Slide 6 - Reverse sales tax - Version B (try independently)</v>
-      </c>
-      <c r="B14" s="114"/>
-      <c r="C14" s="114"/>
-      <c r="D14" s="114"/>
-      <c r="E14" s="114"/>
-      <c r="F14" s="114"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="114"/>
-      <c r="I14" s="114"/>
+      <c r="A14" s="132" t="str">
+        <v>Slide 7 - Reverse sales tax - Version B (try independently)</v>
+      </c>
+      <c r="B14" s="132"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="132"/>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="115" t="str">
+      <c r="A15" s="133" t="str">
         <v>Tidal register receipts of $43,200 include 8% sales tax. Enter the givens, calculate pre-tax sales and tax held, and explain why they add back to receipts.</v>
       </c>
-      <c r="B15" s="115"/>
-      <c r="C15" s="115"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="115"/>
-      <c r="G15" s="115"/>
-      <c r="H15" s="115"/>
-      <c r="I15" s="115"/>
+      <c r="B15" s="133"/>
+      <c r="C15" s="133"/>
+      <c r="D15" s="133"/>
+      <c r="E15" s="133"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="133"/>
+      <c r="I15" s="133"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="116" t="s">
+      <c r="A16" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="116" t="s">
+      <c r="B16" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="116" t="s">
+      <c r="C16" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="116" t="s">
+      <c r="D16" s="134" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="116" t="s">
+      <c r="E16" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="116" t="s">
+      <c r="F16" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="116" t="s">
+      <c r="G16" s="134" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="116" t="s">
+      <c r="H16" s="134" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="116" t="s">
+      <c r="I16" s="134" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="107" t="str">
+      <c r="A17" s="125" t="str">
         <v>B1</v>
       </c>
-      <c r="B17" s="107" t="str">
+      <c r="B17" s="125" t="str">
         <v>Receipts</v>
       </c>
-      <c r="C17" s="107" t="str">
+      <c r="C17" s="125" t="str">
         <v>Enter tax-inclusive receipts 43,200 in D17.</v>
       </c>
-      <c r="D17" s="118"/>
-      <c r="E17" s="110"/>
-      <c r="F17" s="110"/>
-      <c r="G17" s="113"/>
-      <c r="H17" s="107"/>
-      <c r="I17" s="107" t="str">
-        <v>slide 6</v>
+      <c r="D17" s="136"/>
+      <c r="E17" s="128"/>
+      <c r="F17" s="128"/>
+      <c r="G17" s="131"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="125" t="str">
+        <v>slide 7</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="107" t="str">
+      <c r="A18" s="125" t="str">
         <v>B2</v>
       </c>
-      <c r="B18" s="107" t="str">
+      <c r="B18" s="125" t="str">
         <v>Tax rate</v>
       </c>
-      <c r="C18" s="107" t="str">
+      <c r="C18" s="125" t="str">
         <v>Enter sales-tax rate 8% in E18.</v>
       </c>
-      <c r="D18" s="111"/>
-      <c r="E18" s="119"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="113"/>
-      <c r="H18" s="107"/>
-      <c r="I18" s="107" t="str">
-        <v>slide 6</v>
+      <c r="D18" s="129"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="128"/>
+      <c r="G18" s="131"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="125" t="str">
+        <v>slide 7</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="107" t="str">
+      <c r="A19" s="125" t="str">
         <v>B3</v>
       </c>
-      <c r="B19" s="107" t="str">
+      <c r="B19" s="125" t="str">
         <v>Pre-tax sales</v>
       </c>
-      <c r="C19" s="107" t="str">
+      <c r="C19" s="125" t="str">
         <v>Calculate sales before tax in F19 using the two inputs above.</v>
       </c>
-      <c r="D19" s="110"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="113" t="str">
+      <c r="D19" s="128"/>
+      <c r="E19" s="129"/>
+      <c r="F19" s="136"/>
+      <c r="G19" s="131" t="str">
         <f>IF(COUNT(D17,E18,F19)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F19)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D17",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F19)),"$",""))),ISNUMBER(SEARCH("E18",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F19)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F19-40000)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H19" s="107" t="str">
+      <c r="H19" s="125" t="str">
         <v>Explain why the divisor includes 1 plus the tax rate.</v>
       </c>
-      <c r="I19" s="107" t="str">
-        <v>slide 6</v>
+      <c r="I19" s="125" t="str">
+        <v>slide 7</v>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="107" t="str">
+      <c r="A20" s="125" t="str">
         <v>B4</v>
       </c>
-      <c r="B20" s="107" t="str">
+      <c r="B20" s="125" t="str">
         <v>Tax held</v>
       </c>
-      <c r="C20" s="107" t="str">
+      <c r="C20" s="125" t="str">
         <v>Calculate tax held in F20 using receipts and your pre-tax sales result.</v>
       </c>
-      <c r="D20" s="110"/>
-      <c r="E20" s="112"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="113" t="str">
+      <c r="D20" s="128"/>
+      <c r="E20" s="130"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="131" t="str">
         <f>IF(COUNT(D17,F19,F20)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F20)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D17",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F20)),"$",""))),ISNUMBER(SEARCH("F19",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F20)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F20-3200)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H20" s="107" t="str">
+      <c r="H20" s="125" t="str">
         <v>Sales plus tax held must equal receipts.</v>
       </c>
-      <c r="I20" s="107" t="str">
-        <v>slide 6</v>
+      <c r="I20" s="125" t="str">
+        <v>slide 7</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="114" t="str">
-        <v>Continue: sales tax (slide 8), two taxes (slide 13), then property tax (slide 17)</v>
-      </c>
-      <c r="B22" s="114"/>
-      <c r="C22" s="114"/>
-      <c r="D22" s="114"/>
-      <c r="E22" s="114"/>
-      <c r="F22" s="114"/>
-      <c r="G22" s="114"/>
-      <c r="H22" s="114"/>
-      <c r="I22" s="114"/>
+      <c r="A22" s="132" t="str">
+        <v>Continue: sales tax (slide 9), two taxes (slide 14), then property tax (slide 18)</v>
+      </c>
+      <c r="B22" s="132"/>
+      <c r="C22" s="132"/>
+      <c r="D22" s="132"/>
+      <c r="E22" s="132"/>
+      <c r="F22" s="132"/>
+      <c r="G22" s="132"/>
+      <c r="H22" s="132"/>
+      <c r="I22" s="132"/>
     </row>
     <row r="23" ht="16">
       <c r="A23" s="4" t="s">
@@ -2055,7 +2139,7 @@
         <v>30</v>
       </c>
       <c r="I24" s="3" t="str">
-        <v>slide 8</v>
+        <v>slide 9</v>
       </c>
     </row>
     <row r="25" ht="32">
@@ -2079,7 +2163,7 @@
         <v>31</v>
       </c>
       <c r="I25" s="3" t="str">
-        <v>slide 8</v>
+        <v>slide 9</v>
       </c>
     </row>
     <row r="26" ht="32">
@@ -2103,7 +2187,7 @@
         <v>32</v>
       </c>
       <c r="I26" s="3" t="str">
-        <v>slide 8</v>
+        <v>slide 9</v>
       </c>
     </row>
     <row r="27" ht="16">
@@ -2127,7 +2211,7 @@
         <v>35</v>
       </c>
       <c r="I27" s="3" t="str">
-        <v>slide 8</v>
+        <v>slide 9</v>
       </c>
     </row>
     <row r="28" ht="16">
@@ -2151,7 +2235,7 @@
         <v>36</v>
       </c>
       <c r="I28" s="3" t="str">
-        <v>slide 8</v>
+        <v>slide 9</v>
       </c>
     </row>
     <row r="29" ht="32">
@@ -2175,7 +2259,7 @@
         <v>39</v>
       </c>
       <c r="I29" s="3" t="str">
-        <v>slide 13</v>
+        <v>slide 14</v>
       </c>
     </row>
     <row r="30" ht="32">
@@ -2188,7 +2272,7 @@
       <c r="C30" s="3" t="str">
         <v>E: excise rate 4.5%; F: excise tax using the original base in D29.</v>
       </c>
-      <c r="D30" s="120"/>
+      <c r="D30" s="138"/>
       <c r="E30" s="8"/>
       <c r="F30" s="5"/>
       <c r="G30" s="7" t="str">
@@ -2199,7 +2283,7 @@
         <v>Reference the same original base cell used for sales tax: D29.</v>
       </c>
       <c r="I30" s="3" t="str">
-        <v>slide 13</v>
+        <v>slide 14</v>
       </c>
     </row>
     <row r="31" ht="32">
@@ -2212,7 +2296,7 @@
       <c r="C31" s="3" t="str">
         <v>F: total cost using original base D29 and tax results F29 and F30.</v>
       </c>
-      <c r="D31" s="120"/>
+      <c r="D31" s="138"/>
       <c r="E31" s="6"/>
       <c r="F31" s="5"/>
       <c r="G31" s="7" t="str">
@@ -2223,7 +2307,7 @@
         <v>Add the original base and both separate tax results.</v>
       </c>
       <c r="I31" s="3" t="str">
-        <v>slide 13</v>
+        <v>slide 14</v>
       </c>
     </row>
     <row r="32" ht="32">
@@ -2247,7 +2331,7 @@
         <v>42</v>
       </c>
       <c r="I32" s="3" t="str">
-        <v>slide 17</v>
+        <v>slide 18</v>
       </c>
     </row>
     <row r="33" ht="32">
@@ -2271,7 +2355,7 @@
         <v>44</v>
       </c>
       <c r="I33" s="3" t="str">
-        <v>slide 17</v>
+        <v>slide 18</v>
       </c>
     </row>
     <row r="34" ht="32">
@@ -2295,18 +2379,18 @@
         <v>Reference assessed value F32 and rounded rate F33.</v>
       </c>
       <c r="I34" s="3" t="str">
-        <v>slide 17</v>
+        <v>slide 18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A22:I22"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="A14:I14"/>
     <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A22:I22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MATH/M07/bus123-math-m07-l01-starter.xlsx
+++ b/MATH/M07/bus123-math-m07-l01-starter.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R1ad4885203454615" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Rd653915775984c40" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R58c4eb960d8d46b1" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R5c99636da0584474" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R8068b2df7ba34db4" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R62921b1aaac940cc" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R7fb79ac3ac2d4cd5" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="Ra266823d7ee84803" state="visible"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -428,13 +428,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="7">
     <x:numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <x:numFmt numFmtId="165" formatCode="0.0%"/>
     <x:numFmt numFmtId="166" formatCode="0.0000"/>
     <x:numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
     <x:numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
     <x:numFmt numFmtId="169" formatCode="0.00%;[Red]\-0.00%"/>
+    <x:numFmt numFmtId="200" formatCode="0.00%"/>
   </x:numFmts>
   <x:fonts count="16">
     <x:font>
@@ -530,7 +531,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="46">
+  <x:fills count="53">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -615,6 +616,41 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF9C4A2B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2EEE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4A7C5E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFAF8F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF355773"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFD966"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -910,7 +946,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="139">
+  <x:cellXfs count="157">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -1314,6 +1350,58 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="0" fillId="40" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="14" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="47" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="14" fillId="47" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="49" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="51" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="52" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="14" fillId="52" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="14" fillId="52" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="14" fillId="52" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="47" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1795,299 +1883,299 @@
       <c r="I4" s="1"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="132" t="str">
+      <c r="A5" s="149" t="str">
         <v>Slide 7 - Reverse sales tax - Version A (follow along)</v>
       </c>
-      <c r="B5" s="132"/>
-      <c r="C5" s="132"/>
-      <c r="D5" s="132"/>
-      <c r="E5" s="132"/>
-      <c r="F5" s="132"/>
-      <c r="G5" s="132"/>
-      <c r="H5" s="132"/>
-      <c r="I5" s="132"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="149"/>
+      <c r="D5" s="149"/>
+      <c r="E5" s="149"/>
+      <c r="F5" s="149"/>
+      <c r="G5" s="149"/>
+      <c r="H5" s="149"/>
+      <c r="I5" s="149"/>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="133" t="str">
-        <v>Tidal register receipts of $52,000 include 6.5% sales tax. Enter the givens, calculate pre-tax sales and tax held, and explain why they add back to receipts.</v>
-      </c>
-      <c r="B6" s="133"/>
-      <c r="C6" s="133"/>
-      <c r="D6" s="133"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="133"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="133"/>
-      <c r="I6" s="133"/>
+      <c r="A6" s="150" t="str">
+        <v>Tidal register receipts of $52,000 include 6.25% sales tax. Enter the givens, calculate pre-tax sales and tax held, and explain why they add back to receipts.</v>
+      </c>
+      <c r="B6" s="150"/>
+      <c r="C6" s="150"/>
+      <c r="D6" s="150"/>
+      <c r="E6" s="150"/>
+      <c r="F6" s="150"/>
+      <c r="G6" s="150"/>
+      <c r="H6" s="150"/>
+      <c r="I6" s="150"/>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="134" t="s">
+      <c r="A7" s="151" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="134" t="s">
+      <c r="B7" s="151" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="134" t="s">
+      <c r="C7" s="151" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="134" t="s">
+      <c r="D7" s="151" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="134" t="s">
+      <c r="E7" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="134" t="s">
+      <c r="F7" s="151" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="134" t="s">
+      <c r="G7" s="151" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="134" t="s">
+      <c r="H7" s="151" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="134" t="s">
+      <c r="I7" s="151" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="125" t="str">
+      <c r="A8" s="142" t="str">
         <v>A1</v>
       </c>
-      <c r="B8" s="125" t="str">
+      <c r="B8" s="142" t="str">
         <v>Receipts</v>
       </c>
-      <c r="C8" s="125" t="str">
+      <c r="C8" s="142" t="str">
         <v>Enter tax-inclusive receipts 52,000 in D8.</v>
       </c>
-      <c r="D8" s="136"/>
-      <c r="E8" s="128"/>
-      <c r="F8" s="128"/>
-      <c r="G8" s="131"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125" t="str">
+      <c r="D8" s="153"/>
+      <c r="E8" s="145"/>
+      <c r="F8" s="145"/>
+      <c r="G8" s="148"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="142" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="125" t="str">
+      <c r="A9" s="142" t="str">
         <v>A2</v>
       </c>
-      <c r="B9" s="125" t="str">
+      <c r="B9" s="142" t="str">
         <v>Tax rate</v>
       </c>
-      <c r="C9" s="125" t="str">
-        <v>Enter sales-tax rate 6.5% in E9.</v>
-      </c>
-      <c r="D9" s="129"/>
-      <c r="E9" s="137"/>
-      <c r="F9" s="128"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="125"/>
-      <c r="I9" s="125" t="str">
+      <c r="C9" s="142" t="str">
+        <v>Enter sales-tax rate 6.25% in E9.</v>
+      </c>
+      <c r="D9" s="146"/>
+      <c r="E9" s="155"/>
+      <c r="F9" s="145"/>
+      <c r="G9" s="148"/>
+      <c r="H9" s="142"/>
+      <c r="I9" s="142" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="125" t="str">
+      <c r="A10" s="142" t="str">
         <v>A3</v>
       </c>
-      <c r="B10" s="125" t="str">
+      <c r="B10" s="142" t="str">
         <v>Pre-tax sales</v>
       </c>
-      <c r="C10" s="125" t="str">
+      <c r="C10" s="142" t="str">
         <v>Calculate sales before tax in F10 using the two inputs above.</v>
       </c>
-      <c r="D10" s="128"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="136"/>
-      <c r="G10" s="131" t="str">
-        <f>IF(COUNT(D8,E9,F10)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F10)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D8",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F10)),"$",""))),ISNUMBER(SEARCH("E9",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F10)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F10-48826.29107981221)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
+      <c r="D10" s="145"/>
+      <c r="E10" s="146"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="148" t="str">
+        <f>IF(COUNT(D8,E9,F10)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F10)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D8",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F10)),"$",""))),ISNUMBER(SEARCH("E9",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F10)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F10-48941.17647058824)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H10" s="125" t="str">
+      <c r="H10" s="142" t="str">
         <v>Explain why the divisor includes 1 plus the tax rate.</v>
       </c>
-      <c r="I10" s="125" t="str">
+      <c r="I10" s="142" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="125" t="str">
+      <c r="A11" s="142" t="str">
         <v>A4</v>
       </c>
-      <c r="B11" s="125" t="str">
+      <c r="B11" s="142" t="str">
         <v>Tax held</v>
       </c>
-      <c r="C11" s="125" t="str">
+      <c r="C11" s="142" t="str">
         <v>Calculate tax held in F11 using receipts and your pre-tax sales result.</v>
       </c>
-      <c r="D11" s="128"/>
-      <c r="E11" s="130"/>
-      <c r="F11" s="136"/>
-      <c r="G11" s="131" t="str">
-        <f>IF(COUNT(D8,F10,F11)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F11)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D8",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F11)),"$",""))),ISNUMBER(SEARCH("F10",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F11)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F11-3173.7089201877898)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
+      <c r="D11" s="145"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="153"/>
+      <c r="G11" s="148" t="str">
+        <f>IF(COUNT(D8,F10,F11)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F11)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D8",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F11)),"$",""))),ISNUMBER(SEARCH("F10",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F11)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F11-3058.823529411762)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H11" s="125" t="str">
+      <c r="H11" s="142" t="str">
         <v>Sales plus tax held must equal receipts.</v>
       </c>
-      <c r="I11" s="125" t="str">
+      <c r="I11" s="142" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="132" t="str">
+      <c r="A14" s="149" t="str">
         <v>Slide 7 - Reverse sales tax - Version B (try independently)</v>
       </c>
-      <c r="B14" s="132"/>
-      <c r="C14" s="132"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
-      <c r="F14" s="132"/>
-      <c r="G14" s="132"/>
-      <c r="H14" s="132"/>
-      <c r="I14" s="132"/>
+      <c r="B14" s="149"/>
+      <c r="C14" s="149"/>
+      <c r="D14" s="149"/>
+      <c r="E14" s="149"/>
+      <c r="F14" s="149"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="149"/>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="133" t="str">
-        <v>Tidal register receipts of $43,200 include 8% sales tax. Enter the givens, calculate pre-tax sales and tax held, and explain why they add back to receipts.</v>
-      </c>
-      <c r="B15" s="133"/>
-      <c r="C15" s="133"/>
-      <c r="D15" s="133"/>
-      <c r="E15" s="133"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="133"/>
-      <c r="H15" s="133"/>
-      <c r="I15" s="133"/>
+      <c r="A15" s="150" t="str">
+        <v>Tidal register receipts of $43,200 include 6.25% sales tax. Enter the givens, calculate pre-tax sales and tax held, and explain why they add back to receipts.</v>
+      </c>
+      <c r="B15" s="150"/>
+      <c r="C15" s="150"/>
+      <c r="D15" s="150"/>
+      <c r="E15" s="150"/>
+      <c r="F15" s="150"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="150"/>
+      <c r="I15" s="150"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="134" t="s">
+      <c r="A16" s="151" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="134" t="s">
+      <c r="B16" s="151" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="134" t="s">
+      <c r="C16" s="151" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="134" t="s">
+      <c r="D16" s="151" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="134" t="s">
+      <c r="E16" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="134" t="s">
+      <c r="F16" s="151" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="134" t="s">
+      <c r="G16" s="151" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="134" t="s">
+      <c r="H16" s="151" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="134" t="s">
+      <c r="I16" s="151" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="125" t="str">
+      <c r="A17" s="142" t="str">
         <v>B1</v>
       </c>
-      <c r="B17" s="125" t="str">
+      <c r="B17" s="142" t="str">
         <v>Receipts</v>
       </c>
-      <c r="C17" s="125" t="str">
+      <c r="C17" s="142" t="str">
         <v>Enter tax-inclusive receipts 43,200 in D17.</v>
       </c>
-      <c r="D17" s="136"/>
-      <c r="E17" s="128"/>
-      <c r="F17" s="128"/>
-      <c r="G17" s="131"/>
-      <c r="H17" s="125"/>
-      <c r="I17" s="125" t="str">
+      <c r="D17" s="153"/>
+      <c r="E17" s="145"/>
+      <c r="F17" s="145"/>
+      <c r="G17" s="148"/>
+      <c r="H17" s="142"/>
+      <c r="I17" s="142" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="125" t="str">
+      <c r="A18" s="142" t="str">
         <v>B2</v>
       </c>
-      <c r="B18" s="125" t="str">
+      <c r="B18" s="142" t="str">
         <v>Tax rate</v>
       </c>
-      <c r="C18" s="125" t="str">
-        <v>Enter sales-tax rate 8% in E18.</v>
-      </c>
-      <c r="D18" s="129"/>
-      <c r="E18" s="137"/>
-      <c r="F18" s="128"/>
-      <c r="G18" s="131"/>
-      <c r="H18" s="125"/>
-      <c r="I18" s="125" t="str">
+      <c r="C18" s="142" t="str">
+        <v>Enter sales-tax rate 6.25% in E18.</v>
+      </c>
+      <c r="D18" s="146"/>
+      <c r="E18" s="155"/>
+      <c r="F18" s="145"/>
+      <c r="G18" s="148"/>
+      <c r="H18" s="142"/>
+      <c r="I18" s="142" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="125" t="str">
+      <c r="A19" s="142" t="str">
         <v>B3</v>
       </c>
-      <c r="B19" s="125" t="str">
+      <c r="B19" s="142" t="str">
         <v>Pre-tax sales</v>
       </c>
-      <c r="C19" s="125" t="str">
+      <c r="C19" s="142" t="str">
         <v>Calculate sales before tax in F19 using the two inputs above.</v>
       </c>
-      <c r="D19" s="128"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="136"/>
-      <c r="G19" s="131" t="str">
-        <f>IF(COUNT(D17,E18,F19)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F19)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D17",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F19)),"$",""))),ISNUMBER(SEARCH("E18",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F19)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F19-40000)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
+      <c r="D19" s="145"/>
+      <c r="E19" s="146"/>
+      <c r="F19" s="153"/>
+      <c r="G19" s="148" t="str">
+        <f>IF(COUNT(D17,E18,F19)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F19)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D17",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F19)),"$",""))),ISNUMBER(SEARCH("E18",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F19)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F19-40658.82352941176)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H19" s="125" t="str">
+      <c r="H19" s="142" t="str">
         <v>Explain why the divisor includes 1 plus the tax rate.</v>
       </c>
-      <c r="I19" s="125" t="str">
+      <c r="I19" s="142" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="125" t="str">
+      <c r="A20" s="142" t="str">
         <v>B4</v>
       </c>
-      <c r="B20" s="125" t="str">
+      <c r="B20" s="142" t="str">
         <v>Tax held</v>
       </c>
-      <c r="C20" s="125" t="str">
+      <c r="C20" s="142" t="str">
         <v>Calculate tax held in F20 using receipts and your pre-tax sales result.</v>
       </c>
-      <c r="D20" s="128"/>
-      <c r="E20" s="130"/>
-      <c r="F20" s="136"/>
-      <c r="G20" s="131" t="str">
-        <f>IF(COUNT(D17,F19,F20)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F20)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D17",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F20)),"$",""))),ISNUMBER(SEARCH("F19",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F20)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F20-3200)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
+      <c r="D20" s="145"/>
+      <c r="E20" s="147"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="148" t="str">
+        <f>IF(COUNT(D17,F19,F20)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F20)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D17",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F20)),"$",""))),ISNUMBER(SEARCH("F19",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F20)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F20-2541.176470588238)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H20" s="125" t="str">
+      <c r="H20" s="142" t="str">
         <v>Sales plus tax held must equal receipts.</v>
       </c>
-      <c r="I20" s="125" t="str">
+      <c r="I20" s="142" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="132" t="str">
+      <c r="A22" s="149" t="str">
         <v>Continue: sales tax (slide 9), two taxes (slide 14), then property tax (slide 18)</v>
       </c>
-      <c r="B22" s="132"/>
-      <c r="C22" s="132"/>
-      <c r="D22" s="132"/>
-      <c r="E22" s="132"/>
-      <c r="F22" s="132"/>
-      <c r="G22" s="132"/>
-      <c r="H22" s="132"/>
-      <c r="I22" s="132"/>
+      <c r="B22" s="149"/>
+      <c r="C22" s="149"/>
+      <c r="D22" s="149"/>
+      <c r="E22" s="149"/>
+      <c r="F22" s="149"/>
+      <c r="G22" s="149"/>
+      <c r="H22" s="149"/>
+      <c r="I22" s="149"/>
     </row>
     <row r="23" ht="16">
       <c r="A23" s="4" t="s">
@@ -2272,7 +2360,7 @@
       <c r="C30" s="3" t="str">
         <v>E: excise rate 4.5%; F: excise tax using the original base in D29.</v>
       </c>
-      <c r="D30" s="138"/>
+      <c r="D30" s="156"/>
       <c r="E30" s="8"/>
       <c r="F30" s="5"/>
       <c r="G30" s="7" t="str">
@@ -2296,7 +2384,7 @@
       <c r="C31" s="3" t="str">
         <v>F: total cost using original base D29 and tax results F29 and F30.</v>
       </c>
-      <c r="D31" s="138"/>
+      <c r="D31" s="156"/>
       <c r="E31" s="6"/>
       <c r="F31" s="5"/>
       <c r="G31" s="7" t="str">

--- a/MATH/M07/bus123-math-m07-l01-starter.xlsx
+++ b/MATH/M07/bus123-math-m07-l01-starter.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R8068b2df7ba34db4" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R62921b1aaac940cc" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R7fb79ac3ac2d4cd5" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="Ra266823d7ee84803" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Ra2979985246f48f1" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R4773da0f2007449b" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="Rc27a68c00b0f4e19" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R748539a5e78c4a8a" state="visible"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="132">
   <si>
     <t xml:space="preserve">BUS123 - MATH-M07-L01 - Sales, Excise, and Property Taxes</t>
   </si>
@@ -115,9 +115,6 @@
     <t xml:space="preserve">Reverse tax</t>
   </si>
   <si>
-    <t xml:space="preserve">D: receipts 64,200; E: tax rate 7%; F: pre-tax sales.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Divide receipts by 1 plus the tax rate.</t>
   </si>
   <si>
@@ -125,9 +122,6 @@
   </si>
   <si>
     <t xml:space="preserve">Excise tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D: base cost 7,250; E: sales tax rate 6%; F: sales tax.</t>
   </si>
   <si>
     <t xml:space="preserve">Reference the supplied base and sales-tax rate.</t>
@@ -228,16 +222,10 @@
     <t xml:space="preserve">R04</t>
   </si>
   <si>
-    <t xml:space="preserve">Meridian appliance: 7% sales and 8% excise tax share a $6,200 base</t>
-  </si>
-  <si>
     <t xml:space="preserve">=ROUND(D10*(F10+G10),2)</t>
   </si>
   <si>
     <t xml:space="preserve">R05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meridian equipment: 7% sales and 9% excise tax share an $8,400 base</t>
   </si>
   <si>
     <t xml:space="preserve">=ROUND(D11*F11+(D11+D11*F11)*G11,2)</t>
@@ -531,7 +519,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="53">
+  <x:fills count="60">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -616,6 +604,41 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF9C4A2B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2EEE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4A7C5E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFAF8F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF355773"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFD966"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -946,7 +969,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="157">
+  <x:cellXfs count="178">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -1403,6 +1426,67 @@
     </x:xf>
     <x:xf numFmtId="164" fontId="0" fillId="47" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="53" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="53" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="53" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="53" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="53" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="14" fillId="53" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="54" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="54" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="14" fillId="54" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="55" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="56" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="57" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="58" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="59" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="14" fillId="59" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="14" fillId="59" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="14" fillId="59" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="54" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="7" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="7" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1883,299 +1967,299 @@
       <c r="I4" s="1"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="149" t="str">
+      <c r="A5" s="167" t="str">
         <v>Slide 7 - Reverse sales tax - Version A (follow along)</v>
       </c>
-      <c r="B5" s="149"/>
-      <c r="C5" s="149"/>
-      <c r="D5" s="149"/>
-      <c r="E5" s="149"/>
-      <c r="F5" s="149"/>
-      <c r="G5" s="149"/>
-      <c r="H5" s="149"/>
-      <c r="I5" s="149"/>
+      <c r="B5" s="167"/>
+      <c r="C5" s="167"/>
+      <c r="D5" s="167"/>
+      <c r="E5" s="167"/>
+      <c r="F5" s="167"/>
+      <c r="G5" s="167"/>
+      <c r="H5" s="167"/>
+      <c r="I5" s="167"/>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="150" t="str">
+      <c r="A6" s="168" t="str">
         <v>Tidal register receipts of $52,000 include 6.25% sales tax. Enter the givens, calculate pre-tax sales and tax held, and explain why they add back to receipts.</v>
       </c>
-      <c r="B6" s="150"/>
-      <c r="C6" s="150"/>
-      <c r="D6" s="150"/>
-      <c r="E6" s="150"/>
-      <c r="F6" s="150"/>
-      <c r="G6" s="150"/>
-      <c r="H6" s="150"/>
-      <c r="I6" s="150"/>
+      <c r="B6" s="168"/>
+      <c r="C6" s="168"/>
+      <c r="D6" s="168"/>
+      <c r="E6" s="168"/>
+      <c r="F6" s="168"/>
+      <c r="G6" s="168"/>
+      <c r="H6" s="168"/>
+      <c r="I6" s="168"/>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="151" t="s">
+      <c r="A7" s="169" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="151" t="s">
+      <c r="B7" s="169" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="151" t="s">
+      <c r="C7" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="151" t="s">
+      <c r="D7" s="169" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="151" t="s">
+      <c r="E7" s="169" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="151" t="s">
+      <c r="F7" s="169" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="151" t="s">
+      <c r="G7" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="151" t="s">
+      <c r="H7" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="151" t="s">
+      <c r="I7" s="169" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="142" t="str">
+      <c r="A8" s="160" t="str">
         <v>A1</v>
       </c>
-      <c r="B8" s="142" t="str">
+      <c r="B8" s="160" t="str">
         <v>Receipts</v>
       </c>
-      <c r="C8" s="142" t="str">
+      <c r="C8" s="160" t="str">
         <v>Enter tax-inclusive receipts 52,000 in D8.</v>
       </c>
-      <c r="D8" s="153"/>
-      <c r="E8" s="145"/>
-      <c r="F8" s="145"/>
-      <c r="G8" s="148"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="142" t="str">
+      <c r="D8" s="171"/>
+      <c r="E8" s="163"/>
+      <c r="F8" s="163"/>
+      <c r="G8" s="166"/>
+      <c r="H8" s="160"/>
+      <c r="I8" s="160" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="142" t="str">
+      <c r="A9" s="160" t="str">
         <v>A2</v>
       </c>
-      <c r="B9" s="142" t="str">
+      <c r="B9" s="160" t="str">
         <v>Tax rate</v>
       </c>
-      <c r="C9" s="142" t="str">
+      <c r="C9" s="160" t="str">
         <v>Enter sales-tax rate 6.25% in E9.</v>
       </c>
-      <c r="D9" s="146"/>
-      <c r="E9" s="155"/>
-      <c r="F9" s="145"/>
-      <c r="G9" s="148"/>
-      <c r="H9" s="142"/>
-      <c r="I9" s="142" t="str">
+      <c r="D9" s="164"/>
+      <c r="E9" s="173"/>
+      <c r="F9" s="163"/>
+      <c r="G9" s="166"/>
+      <c r="H9" s="160"/>
+      <c r="I9" s="160" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="142" t="str">
+      <c r="A10" s="160" t="str">
         <v>A3</v>
       </c>
-      <c r="B10" s="142" t="str">
+      <c r="B10" s="160" t="str">
         <v>Pre-tax sales</v>
       </c>
-      <c r="C10" s="142" t="str">
+      <c r="C10" s="160" t="str">
         <v>Calculate sales before tax in F10 using the two inputs above.</v>
       </c>
-      <c r="D10" s="145"/>
-      <c r="E10" s="146"/>
-      <c r="F10" s="153"/>
-      <c r="G10" s="148" t="str">
+      <c r="D10" s="163"/>
+      <c r="E10" s="164"/>
+      <c r="F10" s="171"/>
+      <c r="G10" s="166" t="str">
         <f>IF(COUNT(D8,E9,F10)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F10)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D8",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F10)),"$",""))),ISNUMBER(SEARCH("E9",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F10)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F10-48941.17647058824)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H10" s="142" t="str">
+      <c r="H10" s="160" t="str">
         <v>Explain why the divisor includes 1 plus the tax rate.</v>
       </c>
-      <c r="I10" s="142" t="str">
+      <c r="I10" s="160" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="142" t="str">
+      <c r="A11" s="160" t="str">
         <v>A4</v>
       </c>
-      <c r="B11" s="142" t="str">
+      <c r="B11" s="160" t="str">
         <v>Tax held</v>
       </c>
-      <c r="C11" s="142" t="str">
+      <c r="C11" s="160" t="str">
         <v>Calculate tax held in F11 using receipts and your pre-tax sales result.</v>
       </c>
-      <c r="D11" s="145"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="153"/>
-      <c r="G11" s="148" t="str">
+      <c r="D11" s="163"/>
+      <c r="E11" s="165"/>
+      <c r="F11" s="171"/>
+      <c r="G11" s="166" t="str">
         <f>IF(COUNT(D8,F10,F11)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F11)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D8",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F11)),"$",""))),ISNUMBER(SEARCH("F10",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F11)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F11-3058.823529411762)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H11" s="142" t="str">
+      <c r="H11" s="160" t="str">
         <v>Sales plus tax held must equal receipts.</v>
       </c>
-      <c r="I11" s="142" t="str">
+      <c r="I11" s="160" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="149" t="str">
+      <c r="A14" s="167" t="str">
         <v>Slide 7 - Reverse sales tax - Version B (try independently)</v>
       </c>
-      <c r="B14" s="149"/>
-      <c r="C14" s="149"/>
-      <c r="D14" s="149"/>
-      <c r="E14" s="149"/>
-      <c r="F14" s="149"/>
-      <c r="G14" s="149"/>
-      <c r="H14" s="149"/>
-      <c r="I14" s="149"/>
+      <c r="B14" s="167"/>
+      <c r="C14" s="167"/>
+      <c r="D14" s="167"/>
+      <c r="E14" s="167"/>
+      <c r="F14" s="167"/>
+      <c r="G14" s="167"/>
+      <c r="H14" s="167"/>
+      <c r="I14" s="167"/>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="150" t="str">
+      <c r="A15" s="168" t="str">
         <v>Tidal register receipts of $43,200 include 6.25% sales tax. Enter the givens, calculate pre-tax sales and tax held, and explain why they add back to receipts.</v>
       </c>
-      <c r="B15" s="150"/>
-      <c r="C15" s="150"/>
-      <c r="D15" s="150"/>
-      <c r="E15" s="150"/>
-      <c r="F15" s="150"/>
-      <c r="G15" s="150"/>
-      <c r="H15" s="150"/>
-      <c r="I15" s="150"/>
+      <c r="B15" s="168"/>
+      <c r="C15" s="168"/>
+      <c r="D15" s="168"/>
+      <c r="E15" s="168"/>
+      <c r="F15" s="168"/>
+      <c r="G15" s="168"/>
+      <c r="H15" s="168"/>
+      <c r="I15" s="168"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="151" t="s">
+      <c r="A16" s="169" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="151" t="s">
+      <c r="B16" s="169" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="151" t="s">
+      <c r="C16" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="151" t="s">
+      <c r="D16" s="169" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="151" t="s">
+      <c r="E16" s="169" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="151" t="s">
+      <c r="F16" s="169" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="151" t="s">
+      <c r="G16" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="151" t="s">
+      <c r="H16" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="151" t="s">
+      <c r="I16" s="169" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="142" t="str">
+      <c r="A17" s="160" t="str">
         <v>B1</v>
       </c>
-      <c r="B17" s="142" t="str">
+      <c r="B17" s="160" t="str">
         <v>Receipts</v>
       </c>
-      <c r="C17" s="142" t="str">
+      <c r="C17" s="160" t="str">
         <v>Enter tax-inclusive receipts 43,200 in D17.</v>
       </c>
-      <c r="D17" s="153"/>
-      <c r="E17" s="145"/>
-      <c r="F17" s="145"/>
-      <c r="G17" s="148"/>
-      <c r="H17" s="142"/>
-      <c r="I17" s="142" t="str">
+      <c r="D17" s="171"/>
+      <c r="E17" s="163"/>
+      <c r="F17" s="163"/>
+      <c r="G17" s="166"/>
+      <c r="H17" s="160"/>
+      <c r="I17" s="160" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="142" t="str">
+      <c r="A18" s="160" t="str">
         <v>B2</v>
       </c>
-      <c r="B18" s="142" t="str">
+      <c r="B18" s="160" t="str">
         <v>Tax rate</v>
       </c>
-      <c r="C18" s="142" t="str">
+      <c r="C18" s="160" t="str">
         <v>Enter sales-tax rate 6.25% in E18.</v>
       </c>
-      <c r="D18" s="146"/>
-      <c r="E18" s="155"/>
-      <c r="F18" s="145"/>
-      <c r="G18" s="148"/>
-      <c r="H18" s="142"/>
-      <c r="I18" s="142" t="str">
+      <c r="D18" s="164"/>
+      <c r="E18" s="173"/>
+      <c r="F18" s="163"/>
+      <c r="G18" s="166"/>
+      <c r="H18" s="160"/>
+      <c r="I18" s="160" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="142" t="str">
+      <c r="A19" s="160" t="str">
         <v>B3</v>
       </c>
-      <c r="B19" s="142" t="str">
+      <c r="B19" s="160" t="str">
         <v>Pre-tax sales</v>
       </c>
-      <c r="C19" s="142" t="str">
+      <c r="C19" s="160" t="str">
         <v>Calculate sales before tax in F19 using the two inputs above.</v>
       </c>
-      <c r="D19" s="145"/>
-      <c r="E19" s="146"/>
-      <c r="F19" s="153"/>
-      <c r="G19" s="148" t="str">
+      <c r="D19" s="163"/>
+      <c r="E19" s="164"/>
+      <c r="F19" s="171"/>
+      <c r="G19" s="166" t="str">
         <f>IF(COUNT(D17,E18,F19)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F19)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D17",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F19)),"$",""))),ISNUMBER(SEARCH("E18",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F19)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F19-40658.82352941176)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H19" s="142" t="str">
+      <c r="H19" s="160" t="str">
         <v>Explain why the divisor includes 1 plus the tax rate.</v>
       </c>
-      <c r="I19" s="142" t="str">
+      <c r="I19" s="160" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="142" t="str">
+      <c r="A20" s="160" t="str">
         <v>B4</v>
       </c>
-      <c r="B20" s="142" t="str">
+      <c r="B20" s="160" t="str">
         <v>Tax held</v>
       </c>
-      <c r="C20" s="142" t="str">
+      <c r="C20" s="160" t="str">
         <v>Calculate tax held in F20 using receipts and your pre-tax sales result.</v>
       </c>
-      <c r="D20" s="145"/>
-      <c r="E20" s="147"/>
-      <c r="F20" s="153"/>
-      <c r="G20" s="148" t="str">
+      <c r="D20" s="163"/>
+      <c r="E20" s="165"/>
+      <c r="F20" s="171"/>
+      <c r="G20" s="166" t="str">
         <f>IF(COUNT(D17,F19,F20)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F20)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D17",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F20)),"$",""))),ISNUMBER(SEARCH("F19",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F20)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F20-2541.176470588238)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H20" s="142" t="str">
+      <c r="H20" s="160" t="str">
         <v>Sales plus tax held must equal receipts.</v>
       </c>
-      <c r="I20" s="142" t="str">
+      <c r="I20" s="160" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="149" t="str">
+      <c r="A22" s="167" t="str">
         <v>Continue: sales tax (slide 9), two taxes (slide 14), then property tax (slide 18)</v>
       </c>
-      <c r="B22" s="149"/>
-      <c r="C22" s="149"/>
-      <c r="D22" s="149"/>
-      <c r="E22" s="149"/>
-      <c r="F22" s="149"/>
-      <c r="G22" s="149"/>
-      <c r="H22" s="149"/>
-      <c r="I22" s="149"/>
+      <c r="B22" s="167"/>
+      <c r="C22" s="167"/>
+      <c r="D22" s="167"/>
+      <c r="E22" s="167"/>
+      <c r="F22" s="167"/>
+      <c r="G22" s="167"/>
+      <c r="H22" s="167"/>
+      <c r="I22" s="167"/>
     </row>
     <row r="23" ht="16">
       <c r="A23" s="4" t="s">
@@ -2238,13 +2322,13 @@
         <v>28</v>
       </c>
       <c r="C25" s="3" t="str">
-        <v>E: tax rate 5.75%; F: sales tax using subtotal F24.</v>
+        <v>E: tax rate 6.25%; F: sales tax using subtotal F24.</v>
       </c>
       <c r="D25" s="6"/>
-      <c r="E25" s="8"/>
+      <c r="E25" s="175"/>
       <c r="F25" s="5"/>
       <c r="G25" s="7" t="str">
-        <f ca="1">IF(COUNT(F24,E25,F25)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F25)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("F24",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F25)),"$",""))),ISNUMBER(SEARCH("E25",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F25)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(E25-0.0575)&lt;=0.0000001,ABS(F25-36.8)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
+        <f ca="1">IF(COUNT(F24,E25,F25)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F25)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("F24",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F25)),"$",""))),ISNUMBER(SEARCH("E25",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F25)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(E25-0.0625)&lt;=0.0000001,ABS(F25-40)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="H25" s="3" t="s">
@@ -2268,7 +2352,7 @@
       <c r="E26" s="6"/>
       <c r="F26" s="5"/>
       <c r="G26" s="7" t="str">
-        <f ca="1">IF(COUNT(F24,F25,D26,F26)&lt;4,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F26)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("F24",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F26)),"$",""))),ISNUMBER(SEARCH("F25",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F26)),"$",""))),ISNUMBER(SEARCH("D26",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F26)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(D26-22)&lt;=0.01,ABS(F26-698.8)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
+        <f ca="1">IF(COUNT(F24,F25,D26,F26)&lt;4,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F26)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("F24",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F26)),"$",""))),ISNUMBER(SEARCH("F25",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F26)),"$",""))),ISNUMBER(SEARCH("D26",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F26)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(D26-22)&lt;=0.01,ABS(F26-702)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="H26" s="3" t="s">
@@ -2285,18 +2369,18 @@
       <c r="B27" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>34</v>
+      <c r="C27" s="3" t="str">
+        <v>D: receipts 64,200; E: tax rate 6.25%; F: pre-tax sales.</v>
       </c>
       <c r="D27" s="5"/>
-      <c r="E27" s="8"/>
+      <c r="E27" s="175"/>
       <c r="F27" s="5"/>
       <c r="G27" s="7" t="str">
-        <f ca="1">IF(COUNT(D27,E27,F27)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F27)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D27",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F27)),"$",""))),ISNUMBER(SEARCH("E27",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F27)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(D27-64200)&lt;=0.01,ABS(E27-0.07)&lt;=0.0000001,ABS(F27-60000)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
+        <f ca="1">IF(COUNT(D27,E27,F27)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F27)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D27",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F27)),"$",""))),ISNUMBER(SEARCH("E27",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F27)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(D27-64200)&lt;=0.01,ABS(E27-0.0625)&lt;=0.0000001,ABS(F27-60423.529411764706)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I27" s="3" t="str">
         <v>slide 9</v>
@@ -2316,11 +2400,11 @@
       <c r="E28" s="6"/>
       <c r="F28" s="5"/>
       <c r="G28" s="7" t="str">
-        <f ca="1">IF(COUNT(D27,F27,F28)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F28)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D27",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F28)),"$",""))),ISNUMBER(SEARCH("F27",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F28)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(F28-4200)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
+        <f ca="1">IF(COUNT(D27,F27,F28)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F28)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D27",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F28)),"$",""))),ISNUMBER(SEARCH("F27",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F28)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(F28-3776.4705882352937)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I28" s="3" t="str">
         <v>slide 9</v>
@@ -2331,20 +2415,20 @@
         <v>6</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="C29" s="3" t="str">
+        <v>D: base cost 7,250; E: sales tax rate 6.25%; F: sales tax.</v>
       </c>
       <c r="D29" s="5"/>
-      <c r="E29" s="8"/>
+      <c r="E29" s="175"/>
       <c r="F29" s="5"/>
       <c r="G29" s="7" t="str">
-        <f ca="1">IF(COUNT(D29,E29,F29)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F29)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D29",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F29)),"$",""))),ISNUMBER(SEARCH("E29",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F29)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(D29-7250)&lt;=0.01,ABS(E29-0.06)&lt;=0.0000001,ABS(F29-435)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
+        <f ca="1">IF(COUNT(D29,E29,F29)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F29)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D29",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F29)),"$",""))),ISNUMBER(SEARCH("E29",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F29)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(D29-7250)&lt;=0.01,ABS(E29-0.0625)&lt;=0.0000001,ABS(F29-453.125)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I29" s="3" t="str">
         <v>slide 14</v>
@@ -2355,12 +2439,12 @@
         <v>7</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="3" t="str">
         <v>E: excise rate 4.5%; F: excise tax using the original base in D29.</v>
       </c>
-      <c r="D30" s="156"/>
+      <c r="D30" s="174"/>
       <c r="E30" s="8"/>
       <c r="F30" s="5"/>
       <c r="G30" s="7" t="str">
@@ -2379,16 +2463,16 @@
         <v>8</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C31" s="3" t="str">
         <v>F: total cost using original base D29 and tax results F29 and F30.</v>
       </c>
-      <c r="D31" s="156"/>
+      <c r="D31" s="174"/>
       <c r="E31" s="6"/>
       <c r="F31" s="5"/>
       <c r="G31" s="7" t="str">
-        <f ca="1">IF(COUNT(D29,F29,F30,F31)&lt;4,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F31)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D29",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F31)),"$",""))),ISNUMBER(SEARCH("F29",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F31)),"$",""))),ISNUMBER(SEARCH("F30",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F31)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(F31-8011.25)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
+        <f ca="1">IF(COUNT(D29,F29,F30,F31)&lt;4,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F31)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D29",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F31)),"$",""))),ISNUMBER(SEARCH("F29",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F31)),"$",""))),ISNUMBER(SEARCH("F30",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F31)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(F31-8029.374999999999)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="H31" s="3" t="str">
@@ -2403,10 +2487,10 @@
         <v>9</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="8"/>
@@ -2416,7 +2500,7 @@
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I32" s="3" t="str">
         <v>slide 18</v>
@@ -2427,10 +2511,10 @@
         <v>10</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
@@ -2440,7 +2524,7 @@
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I33" s="3" t="str">
         <v>slide 18</v>
@@ -2451,7 +2535,7 @@
         <v>11</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C34" s="3" t="str">
         <v>F: annual tax due using assessed value F32 and rounded rate F33.</v>
@@ -2504,7 +2588,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="66" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="66"/>
@@ -2550,7 +2634,7 @@
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="68" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B4" s="68"/>
       <c r="C4" s="68"/>
@@ -2566,7 +2650,7 @@
     </row>
     <row r="5">
       <c r="A5" s="69" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -2577,58 +2661,58 @@
       <c r="H5" s="70"/>
       <c r="I5" s="71"/>
       <c r="J5" s="72" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K5" s="73"/>
       <c r="L5" s="74"/>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="D6" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="E6" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="F6" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="G6" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="H6" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="I6" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="J6" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="K6" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="L6" s="17" t="s">
         <v>58</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D7" s="30">
         <v>1200</v>
@@ -2636,12 +2720,12 @@
       <c r="E7" s="30">
         <v>180</v>
       </c>
-      <c r="F7" s="39">
-        <v>6.25E-2</v>
+      <c r="F7" s="176" t="n">
+        <v>0.0625</v>
       </c>
       <c r="G7" s="39"/>
       <c r="H7" s="27" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I7" s="30" t="n">
         <f>ROUND((D7-E7)*F7,2)</f>
@@ -2653,13 +2737,13 @@
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D8" s="31">
         <v>480</v>
@@ -2667,16 +2751,16 @@
       <c r="E8" s="31">
         <v>80</v>
       </c>
-      <c r="F8" s="40">
-        <v>0.06</v>
+      <c r="F8" s="177" t="n">
+        <v>0.0625</v>
       </c>
       <c r="G8" s="40"/>
       <c r="H8" s="28" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I8" s="31" t="n">
         <f>ROUND(D8*F8,2)</f>
-        <v>28.8</v>
+        <v>30</v>
       </c>
       <c r="J8" s="21"/>
       <c r="K8" s="35"/>
@@ -2684,24 +2768,24 @@
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>28</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D9" s="31">
         <v>78625</v>
       </c>
       <c r="E9" s="40"/>
-      <c r="F9" s="40">
-        <v>6.25E-2</v>
+      <c r="F9" s="177" t="n">
+        <v>0.0625</v>
       </c>
       <c r="G9" s="40"/>
       <c r="H9" s="28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I9" s="31" t="n">
         <f>ROUND(D9-D9/(1+F9),2)</f>
@@ -2713,30 +2797,30 @@
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>71</v>
+        <v>36</v>
+      </c>
+      <c r="C10" s="25" t="str">
+        <v>Meridian appliance: 6.25% sales and 8% supplied excise tax share a $6,200 base</v>
       </c>
       <c r="D10" s="31">
         <v>6200</v>
       </c>
       <c r="E10" s="40"/>
-      <c r="F10" s="40">
-        <v>7.0000000000000007E-2</v>
+      <c r="F10" s="177" t="n">
+        <v>0.0625</v>
       </c>
       <c r="G10" s="40">
         <v>0.08</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I10" s="31" t="n">
         <f>ROUND(D10*(F10+G10),2)</f>
-        <v>930</v>
+        <v>883.5</v>
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="35"/>
@@ -2744,30 +2828,30 @@
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="20" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>74</v>
+        <v>36</v>
+      </c>
+      <c r="C11" s="25" t="str">
+        <v>Meridian equipment: 6.25% sales and 9% supplied excise tax share an $8,400 base</v>
       </c>
       <c r="D11" s="31">
         <v>8400</v>
       </c>
       <c r="E11" s="40"/>
-      <c r="F11" s="40">
-        <v>7.0000000000000007E-2</v>
+      <c r="F11" s="177" t="n">
+        <v>0.0625</v>
       </c>
       <c r="G11" s="40">
         <v>0.09</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I11" s="31" t="n">
         <f>ROUND(D11*F11+(D11+D11*F11)*G11,2)</f>
-        <v>1396.92</v>
+        <v>1328.25</v>
       </c>
       <c r="J11" s="21"/>
       <c r="K11" s="35"/>
@@ -2775,13 +2859,13 @@
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="22" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D12" s="32">
         <v>820000</v>
@@ -2796,7 +2880,7 @@
         <v>4750000</v>
       </c>
       <c r="H12" s="29" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I12" s="32" t="n">
         <f>ROUND(D12*ROUND(F12/G12,4),2)</f>
@@ -2836,7 +2920,7 @@
     </row>
     <row r="15">
       <c r="A15" s="75" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B15" s="76"/>
       <c r="C15" s="76"/>
@@ -2852,24 +2936,24 @@
     </row>
     <row r="16">
       <c r="A16" s="82" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B16" s="83"/>
       <c r="C16" s="83"/>
       <c r="D16" s="30" t="n">
         <f>SUM(I7:I12)</f>
-        <v>60590.47</v>
+        <v>60476.5</v>
       </c>
       <c r="E16" s="83" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F16" s="83"/>
       <c r="G16" s="83"/>
-      <c r="H16" s="30">
-        <v>28405.15</v>
+      <c r="H16" s="30" t="n">
+        <v>28296.65</v>
       </c>
       <c r="I16" s="84" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="J16" s="84"/>
       <c r="K16" s="34"/>
@@ -2885,7 +2969,7 @@
       <c r="G17" s="42"/>
       <c r="H17" s="42"/>
       <c r="I17" s="85" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J17" s="85"/>
       <c r="K17" s="36"/>
@@ -2901,7 +2985,7 @@
       <c r="G18" s="42"/>
       <c r="H18" s="42"/>
       <c r="I18" s="85" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J18" s="85"/>
       <c r="K18" s="36"/>
@@ -2917,7 +3001,7 @@
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
       <c r="I19" s="61" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J19" s="61"/>
       <c r="K19" s="43"/>
@@ -2939,7 +3023,7 @@
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="62" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B21" s="63"/>
       <c r="C21" s="63"/>
@@ -3033,7 +3117,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="55" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B1" s="56"/>
       <c r="C1" s="56"/>
@@ -3047,170 +3131,170 @@
     </row>
     <row r="3" ht="16">
       <c r="A3" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" ht="32">
       <c r="A4" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" ht="32">
       <c r="A5" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" ht="16">
       <c r="A6" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" ht="16">
       <c r="A7" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" ht="16">
       <c r="A8" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" ht="32">
       <c r="A9" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" ht="32">
       <c r="A10" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" ht="32">
       <c r="A11" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" ht="32">
       <c r="A12" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" ht="16">
       <c r="A13" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" ht="32">
       <c r="A14" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/MATH/M07/bus123-math-m07-l01-starter.xlsx
+++ b/MATH/M07/bus123-math-m07-l01-starter.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Ra2979985246f48f1" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R4773da0f2007449b" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="Rc27a68c00b0f4e19" state="visible"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R748539a5e78c4a8a" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Red74cf7128864026" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R08a59116077b4b04" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="Rbdf7b202e09744a7" state="visible"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R8a18ea6f8a8f4d91" state="visible"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="93">
   <si>
     <t xml:space="preserve">BUS123 - MATH-M07-L01 - Sales, Excise, and Property Taxes</t>
   </si>
@@ -121,33 +121,12 @@
     <t xml:space="preserve">Reference receipts and pre-tax sales.</t>
   </si>
   <si>
-    <t xml:space="preserve">Excise tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference the supplied base and sales-tax rate.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Property tax</t>
   </si>
   <si>
-    <t xml:space="preserve">D: market value 540,000; E: assessment rate 32%; F: assessed value.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference market value and the supplied assessment rate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D: town budget 234,500; E: total assessed value 3,450,000; F: rounded rate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use ROUND on budget divided by total assessed value.</t>
-  </si>
-  <si>
     <t xml:space="preserve">MATH-M07 - Class Challenge | Tax Compliance Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">All cases use the supplied training-jurisdiction rules. Blue-gray cells are source data and stay unchanged. Yellow cells are your audit work. Corrected liabilities must be formulas, not typed answers.</t>
-  </si>
-  <si>
     <t xml:space="preserve">SUPPLIED SOURCE DATA + FILED CALCULATION</t>
   </si>
   <si>
@@ -161,15 +140,6 @@
   </si>
   <si>
     <t xml:space="preserve">Audit case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amount / market value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discount / assessment rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tax rate / town budget</t>
   </si>
   <si>
     <t xml:space="preserve">Second rate / total AV</t>
@@ -198,46 +168,25 @@
     <t xml:space="preserve">Tidal invoice: $1,200 less $180 trade discount; tax liability only</t>
   </si>
   <si>
-    <t xml:space="preserve">=ROUND((D7-E7)*F7,2)</t>
-  </si>
-  <si>
     <t xml:space="preserve">R02</t>
   </si>
   <si>
     <t xml:space="preserve">Tidal order: $480 less $80 trade discount; tax liability only</t>
   </si>
   <si>
-    <t xml:space="preserve">=ROUND(D8*F8,2)</t>
-  </si>
-  <si>
     <t xml:space="preserve">R03</t>
   </si>
   <si>
     <t xml:space="preserve">Tidal register: tax is included in $78,625 total receipts</t>
   </si>
   <si>
-    <t xml:space="preserve">=ROUND(D9-D9/(1+F9),2)</t>
-  </si>
-  <si>
     <t xml:space="preserve">R04</t>
   </si>
   <si>
-    <t xml:space="preserve">=ROUND(D10*(F10+G10),2)</t>
-  </si>
-  <si>
     <t xml:space="preserve">R05</t>
   </si>
   <si>
-    <t xml:space="preserve">=ROUND(D11*F11+(D11+D11*F11)*G11,2)</t>
-  </si>
-  <si>
     <t xml:space="preserve">R06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meridian office: annual property tax using assessed value and a 4-decimal rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">=ROUND(D12*ROUND(F12/G12,4),2)</t>
   </si>
   <si>
     <t xml:space="preserve">LIABILITY RECONCILIATION</t>
@@ -340,83 +289,17 @@
     <t xml:space="preserve">Collected tax is a liability, not revenue.</t>
   </si>
   <si>
-    <t xml:space="preserve">Separate excise taxes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">=Base*SalesRate and =Base*ExciseRate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calculates both tax amounts from the same base.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use only when the scenario says both taxes share one base.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combined excise shortcut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">=Base*(1+SalesRate+ExciseRate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combines rates when they share one base.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The shortcut is valid only under the supplied same-base rule.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assessed value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">=MarketValue*AssessmentRate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Converts market value to taxable assessed value.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use the assessment rule supplied by the training municipality.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Property tax rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">=ROUND(Budget/TotalAV,4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rounds the municipal tax rate to four decimals.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Round the rate before applying it to assessed value.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annual property tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">=RoundedRate*AssessedValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calculates annual property tax due.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use assessed value and the rounded rate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly NNN reserve</t>
-  </si>
-  <si>
     <t xml:space="preserve">=AnnualTax/12</t>
   </si>
   <si>
     <t xml:space="preserve">Converts annual property tax into monthly planning cost.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use for lease cash-flow planning; actual obligations depend on lease terms.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="7">
+  <x:numFmts count="10">
     <x:numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <x:numFmt numFmtId="165" formatCode="0.0%"/>
     <x:numFmt numFmtId="166" formatCode="0.0000"/>
@@ -424,6 +307,9 @@
     <x:numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
     <x:numFmt numFmtId="169" formatCode="0.00%;[Red]\-0.00%"/>
     <x:numFmt numFmtId="200" formatCode="0.00%"/>
+    <x:numFmt numFmtId="201" formatCode="&quot;$&quot;0.00"/>
+    <x:numFmt numFmtId="202" formatCode="0%"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="16">
     <x:font>
@@ -519,7 +405,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="60">
+  <x:fills count="74">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -604,6 +490,76 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF9C4A2B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2EEE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4A7C5E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFAF8F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF355773"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFD966"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2EEE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4A7C5E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFAF8F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF355773"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFD966"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -969,7 +925,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="178">
+  <x:cellXfs count="224">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -1487,6 +1443,140 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="7" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="60" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="60" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="60" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="60" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="60" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="14" fillId="60" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="61" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="61" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="14" fillId="61" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="62" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="65" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="66" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="14" fillId="66" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="14" fillId="66" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="61" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="61" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="66" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="66" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="7" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="7" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="67" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="67" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="67" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="67" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="67" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="14" fillId="67" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="68" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="68" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="14" fillId="68" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="69" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="71" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="72" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="73" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="14" fillId="73" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="14" fillId="73" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="68" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="68" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="68" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="73" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="7" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1801,7 +1891,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="3" t="str">
-        <v>Start with slide 7: Version A in rows 8-11, then Version B in rows 17-20. Continue downward: sales tax on slide 9 (rows 24-28), two taxes on slide 14 (rows 29-31), and property tax on slide 18 (rows 32-34).</v>
+        <v>Start with slide 7: Version A in rows 8-11, then Version B in rows 17-20. Continue downward: sales tax on slide 9 (rows 24-28), vehicle excise on slide 14 (rows 29-31), and property tax on slide 18 (rows 32-34).</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1967,299 +2057,299 @@
       <c r="I4" s="1"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="167" t="str">
+      <c r="A5" s="210" t="str">
         <v>Slide 7 - Reverse sales tax - Version A (follow along)</v>
       </c>
-      <c r="B5" s="167"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
-      <c r="F5" s="167"/>
-      <c r="G5" s="167"/>
-      <c r="H5" s="167"/>
-      <c r="I5" s="167"/>
+      <c r="B5" s="210"/>
+      <c r="C5" s="210"/>
+      <c r="D5" s="210"/>
+      <c r="E5" s="210"/>
+      <c r="F5" s="210"/>
+      <c r="G5" s="210"/>
+      <c r="H5" s="210"/>
+      <c r="I5" s="210"/>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="168" t="str">
+      <c r="A6" s="211" t="str">
         <v>Tidal register receipts of $52,000 include 6.25% sales tax. Enter the givens, calculate pre-tax sales and tax held, and explain why they add back to receipts.</v>
       </c>
-      <c r="B6" s="168"/>
-      <c r="C6" s="168"/>
-      <c r="D6" s="168"/>
-      <c r="E6" s="168"/>
-      <c r="F6" s="168"/>
-      <c r="G6" s="168"/>
-      <c r="H6" s="168"/>
-      <c r="I6" s="168"/>
+      <c r="B6" s="211"/>
+      <c r="C6" s="211"/>
+      <c r="D6" s="211"/>
+      <c r="E6" s="211"/>
+      <c r="F6" s="211"/>
+      <c r="G6" s="211"/>
+      <c r="H6" s="211"/>
+      <c r="I6" s="211"/>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="169" t="s">
+      <c r="A7" s="212" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="169" t="s">
+      <c r="B7" s="212" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="169" t="s">
+      <c r="C7" s="212" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="169" t="s">
+      <c r="D7" s="212" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="169" t="s">
+      <c r="E7" s="212" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="169" t="s">
+      <c r="F7" s="212" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="169" t="s">
+      <c r="G7" s="212" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="169" t="s">
+      <c r="H7" s="212" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="169" t="s">
+      <c r="I7" s="212" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="160" t="str">
+      <c r="A8" s="203" t="str">
         <v>A1</v>
       </c>
-      <c r="B8" s="160" t="str">
+      <c r="B8" s="203" t="str">
         <v>Receipts</v>
       </c>
-      <c r="C8" s="160" t="str">
+      <c r="C8" s="203" t="str">
         <v>Enter tax-inclusive receipts 52,000 in D8.</v>
       </c>
-      <c r="D8" s="171"/>
-      <c r="E8" s="163"/>
-      <c r="F8" s="163"/>
-      <c r="G8" s="166"/>
-      <c r="H8" s="160"/>
-      <c r="I8" s="160" t="str">
+      <c r="D8" s="214"/>
+      <c r="E8" s="206"/>
+      <c r="F8" s="206"/>
+      <c r="G8" s="209"/>
+      <c r="H8" s="203"/>
+      <c r="I8" s="203" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="160" t="str">
+      <c r="A9" s="203" t="str">
         <v>A2</v>
       </c>
-      <c r="B9" s="160" t="str">
+      <c r="B9" s="203" t="str">
         <v>Tax rate</v>
       </c>
-      <c r="C9" s="160" t="str">
+      <c r="C9" s="203" t="str">
         <v>Enter sales-tax rate 6.25% in E9.</v>
       </c>
-      <c r="D9" s="164"/>
-      <c r="E9" s="173"/>
-      <c r="F9" s="163"/>
-      <c r="G9" s="166"/>
-      <c r="H9" s="160"/>
-      <c r="I9" s="160" t="str">
+      <c r="D9" s="207"/>
+      <c r="E9" s="215"/>
+      <c r="F9" s="206"/>
+      <c r="G9" s="209"/>
+      <c r="H9" s="203"/>
+      <c r="I9" s="203" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="160" t="str">
+      <c r="A10" s="203" t="str">
         <v>A3</v>
       </c>
-      <c r="B10" s="160" t="str">
+      <c r="B10" s="203" t="str">
         <v>Pre-tax sales</v>
       </c>
-      <c r="C10" s="160" t="str">
+      <c r="C10" s="203" t="str">
         <v>Calculate sales before tax in F10 using the two inputs above.</v>
       </c>
-      <c r="D10" s="163"/>
-      <c r="E10" s="164"/>
-      <c r="F10" s="171"/>
-      <c r="G10" s="166" t="str">
+      <c r="D10" s="206"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="214"/>
+      <c r="G10" s="209" t="str">
         <f>IF(COUNT(D8,E9,F10)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F10)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D8",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F10)),"$",""))),ISNUMBER(SEARCH("E9",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F10)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F10-48941.17647058824)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H10" s="160" t="str">
+      <c r="H10" s="203" t="str">
         <v>Explain why the divisor includes 1 plus the tax rate.</v>
       </c>
-      <c r="I10" s="160" t="str">
+      <c r="I10" s="203" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="160" t="str">
+      <c r="A11" s="203" t="str">
         <v>A4</v>
       </c>
-      <c r="B11" s="160" t="str">
+      <c r="B11" s="203" t="str">
         <v>Tax held</v>
       </c>
-      <c r="C11" s="160" t="str">
+      <c r="C11" s="203" t="str">
         <v>Calculate tax held in F11 using receipts and your pre-tax sales result.</v>
       </c>
-      <c r="D11" s="163"/>
-      <c r="E11" s="165"/>
-      <c r="F11" s="171"/>
-      <c r="G11" s="166" t="str">
+      <c r="D11" s="206"/>
+      <c r="E11" s="208"/>
+      <c r="F11" s="214"/>
+      <c r="G11" s="209" t="str">
         <f>IF(COUNT(D8,F10,F11)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F11)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D8",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F11)),"$",""))),ISNUMBER(SEARCH("F10",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F11)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F11-3058.823529411762)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H11" s="160" t="str">
+      <c r="H11" s="203" t="str">
         <v>Sales plus tax held must equal receipts.</v>
       </c>
-      <c r="I11" s="160" t="str">
+      <c r="I11" s="203" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="167" t="str">
+      <c r="A14" s="210" t="str">
         <v>Slide 7 - Reverse sales tax - Version B (try independently)</v>
       </c>
-      <c r="B14" s="167"/>
-      <c r="C14" s="167"/>
-      <c r="D14" s="167"/>
-      <c r="E14" s="167"/>
-      <c r="F14" s="167"/>
-      <c r="G14" s="167"/>
-      <c r="H14" s="167"/>
-      <c r="I14" s="167"/>
+      <c r="B14" s="210"/>
+      <c r="C14" s="210"/>
+      <c r="D14" s="210"/>
+      <c r="E14" s="210"/>
+      <c r="F14" s="210"/>
+      <c r="G14" s="210"/>
+      <c r="H14" s="210"/>
+      <c r="I14" s="210"/>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="168" t="str">
+      <c r="A15" s="211" t="str">
         <v>Tidal register receipts of $43,200 include 6.25% sales tax. Enter the givens, calculate pre-tax sales and tax held, and explain why they add back to receipts.</v>
       </c>
-      <c r="B15" s="168"/>
-      <c r="C15" s="168"/>
-      <c r="D15" s="168"/>
-      <c r="E15" s="168"/>
-      <c r="F15" s="168"/>
-      <c r="G15" s="168"/>
-      <c r="H15" s="168"/>
-      <c r="I15" s="168"/>
+      <c r="B15" s="211"/>
+      <c r="C15" s="211"/>
+      <c r="D15" s="211"/>
+      <c r="E15" s="211"/>
+      <c r="F15" s="211"/>
+      <c r="G15" s="211"/>
+      <c r="H15" s="211"/>
+      <c r="I15" s="211"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="169" t="s">
+      <c r="A16" s="212" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="169" t="s">
+      <c r="B16" s="212" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="169" t="s">
+      <c r="C16" s="212" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="169" t="s">
+      <c r="D16" s="212" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="169" t="s">
+      <c r="E16" s="212" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="169" t="s">
+      <c r="F16" s="212" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="169" t="s">
+      <c r="G16" s="212" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="169" t="s">
+      <c r="H16" s="212" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="169" t="s">
+      <c r="I16" s="212" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="160" t="str">
+      <c r="A17" s="203" t="str">
         <v>B1</v>
       </c>
-      <c r="B17" s="160" t="str">
+      <c r="B17" s="203" t="str">
         <v>Receipts</v>
       </c>
-      <c r="C17" s="160" t="str">
+      <c r="C17" s="203" t="str">
         <v>Enter tax-inclusive receipts 43,200 in D17.</v>
       </c>
-      <c r="D17" s="171"/>
-      <c r="E17" s="163"/>
-      <c r="F17" s="163"/>
-      <c r="G17" s="166"/>
-      <c r="H17" s="160"/>
-      <c r="I17" s="160" t="str">
+      <c r="D17" s="214"/>
+      <c r="E17" s="206"/>
+      <c r="F17" s="206"/>
+      <c r="G17" s="209"/>
+      <c r="H17" s="203"/>
+      <c r="I17" s="203" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="160" t="str">
+      <c r="A18" s="203" t="str">
         <v>B2</v>
       </c>
-      <c r="B18" s="160" t="str">
+      <c r="B18" s="203" t="str">
         <v>Tax rate</v>
       </c>
-      <c r="C18" s="160" t="str">
+      <c r="C18" s="203" t="str">
         <v>Enter sales-tax rate 6.25% in E18.</v>
       </c>
-      <c r="D18" s="164"/>
-      <c r="E18" s="173"/>
-      <c r="F18" s="163"/>
-      <c r="G18" s="166"/>
-      <c r="H18" s="160"/>
-      <c r="I18" s="160" t="str">
+      <c r="D18" s="207"/>
+      <c r="E18" s="215"/>
+      <c r="F18" s="206"/>
+      <c r="G18" s="209"/>
+      <c r="H18" s="203"/>
+      <c r="I18" s="203" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="160" t="str">
+      <c r="A19" s="203" t="str">
         <v>B3</v>
       </c>
-      <c r="B19" s="160" t="str">
+      <c r="B19" s="203" t="str">
         <v>Pre-tax sales</v>
       </c>
-      <c r="C19" s="160" t="str">
+      <c r="C19" s="203" t="str">
         <v>Calculate sales before tax in F19 using the two inputs above.</v>
       </c>
-      <c r="D19" s="163"/>
-      <c r="E19" s="164"/>
-      <c r="F19" s="171"/>
-      <c r="G19" s="166" t="str">
+      <c r="D19" s="206"/>
+      <c r="E19" s="207"/>
+      <c r="F19" s="214"/>
+      <c r="G19" s="209" t="str">
         <f>IF(COUNT(D17,E18,F19)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F19)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D17",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F19)),"$",""))),ISNUMBER(SEARCH("E18",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F19)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F19-40658.82352941176)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H19" s="160" t="str">
+      <c r="H19" s="203" t="str">
         <v>Explain why the divisor includes 1 plus the tax rate.</v>
       </c>
-      <c r="I19" s="160" t="str">
+      <c r="I19" s="203" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="160" t="str">
+      <c r="A20" s="203" t="str">
         <v>B4</v>
       </c>
-      <c r="B20" s="160" t="str">
+      <c r="B20" s="203" t="str">
         <v>Tax held</v>
       </c>
-      <c r="C20" s="160" t="str">
+      <c r="C20" s="203" t="str">
         <v>Calculate tax held in F20 using receipts and your pre-tax sales result.</v>
       </c>
-      <c r="D20" s="163"/>
-      <c r="E20" s="165"/>
-      <c r="F20" s="171"/>
-      <c r="G20" s="166" t="str">
+      <c r="D20" s="206"/>
+      <c r="E20" s="208"/>
+      <c r="F20" s="214"/>
+      <c r="G20" s="209" t="str">
         <f>IF(COUNT(D17,F19,F20)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F20)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D17",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F20)),"$",""))),ISNUMBER(SEARCH("F19",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F20)),"$","")))),FALSE)),"Use the required input/result references",IF(ABS(F20-2541.176470588238)&lt;=0.01,"Correct - explain your revenue/tax split","Check the inputs and reverse-tax calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H20" s="160" t="str">
+      <c r="H20" s="203" t="str">
         <v>Sales plus tax held must equal receipts.</v>
       </c>
-      <c r="I20" s="160" t="str">
+      <c r="I20" s="203" t="str">
         <v>slide 7</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="167" t="str">
-        <v>Continue: sales tax (slide 9), two taxes (slide 14), then property tax (slide 18)</v>
-      </c>
-      <c r="B22" s="167"/>
-      <c r="C22" s="167"/>
-      <c r="D22" s="167"/>
-      <c r="E22" s="167"/>
-      <c r="F22" s="167"/>
-      <c r="G22" s="167"/>
-      <c r="H22" s="167"/>
-      <c r="I22" s="167"/>
+      <c r="A22" s="210" t="str">
+        <v>Continue: sales tax (slide 9), vehicle excise (slide 14), then property tax (slide 18)</v>
+      </c>
+      <c r="B22" s="210"/>
+      <c r="C22" s="210"/>
+      <c r="D22" s="210"/>
+      <c r="E22" s="210"/>
+      <c r="F22" s="210"/>
+      <c r="G22" s="210"/>
+      <c r="H22" s="210"/>
+      <c r="I22" s="210"/>
     </row>
     <row r="23" ht="16">
       <c r="A23" s="4" t="s">
@@ -2414,21 +2504,21 @@
       <c r="A29" s="3">
         <v>6</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>36</v>
+      <c r="B29" s="3" t="str">
+        <v>Vehicle excise</v>
       </c>
       <c r="C29" s="3" t="str">
-        <v>D: base cost 7,250; E: sales tax rate 6.25%; F: sales tax.</v>
+        <v>D: original list price 30,000; E: third-year value percentage 40%; F: excise value.</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="175"/>
       <c r="F29" s="5"/>
       <c r="G29" s="7" t="str">
-        <f ca="1">IF(COUNT(D29,E29,F29)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F29)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D29",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F29)),"$",""))),ISNUMBER(SEARCH("E29",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F29)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(D29-7250)&lt;=0.01,ABS(E29-0.0625)&lt;=0.0000001,ABS(F29-453.125)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
+        <f ca="1">IF(COUNT(D29,E29,F29)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F29)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D29",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F29)),"$",""))),ISNUMBER(SEARCH("E29",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F29)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(D29-30000)&lt;=0.01,ABS(E29-0.4)&lt;=0.0000001,ABS(F29-12000)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>37</v>
+      <c r="H29" s="3" t="str">
+        <v>Use the manufacturer’s original list price, not purchase price.</v>
       </c>
       <c r="I29" s="3" t="str">
         <v>slide 14</v>
@@ -2438,21 +2528,21 @@
       <c r="A30" s="3">
         <v>7</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>36</v>
+      <c r="B30" s="3" t="str">
+        <v>Vehicle excise</v>
       </c>
       <c r="C30" s="3" t="str">
-        <v>E: excise rate 4.5%; F: excise tax using the original base in D29.</v>
-      </c>
-      <c r="D30" s="174"/>
-      <c r="E30" s="8"/>
+        <v>D: $25 per $1,000; F: annual vehicle excise using excise value F29.</v>
+      </c>
+      <c r="D30" s="219"/>
+      <c r="E30" s="218"/>
       <c r="F30" s="5"/>
       <c r="G30" s="7" t="str">
-        <f ca="1">IF(COUNT(D29,E30,F30)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F30)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D29",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F30)),"$",""))),ISNUMBER(SEARCH("E30",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F30)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(E30-0.045)&lt;=0.0000001,ABS(F30-326.25)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
+        <f ca="1">IF(COUNT(F29,D30,F30)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F30)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("F29",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F30)),"$",""))),ISNUMBER(SEARCH("D30",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F30)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(D30-25)&lt;=0.01,ABS(F30-300)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="H30" s="3" t="str">
-        <v>Reference the same original base cell used for sales tax: D29.</v>
+        <v>Divide excise value F29 by 1,000, then multiply by the dollar rate D30.</v>
       </c>
       <c r="I30" s="3" t="str">
         <v>slide 14</v>
@@ -2462,21 +2552,21 @@
       <c r="A31" s="3">
         <v>8</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>36</v>
+      <c r="B31" s="3" t="str">
+        <v>Vehicle excise</v>
       </c>
       <c r="C31" s="3" t="str">
-        <v>F: total cost using original base D29 and tax results F29 and F30.</v>
-      </c>
-      <c r="D31" s="174"/>
+        <v>F: monthly amount to set aside using annual excise F30.</v>
+      </c>
+      <c r="D31" s="217"/>
       <c r="E31" s="6"/>
       <c r="F31" s="5"/>
       <c r="G31" s="7" t="str">
-        <f ca="1">IF(COUNT(D29,F29,F30,F31)&lt;4,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F31)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D29",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F31)),"$",""))),ISNUMBER(SEARCH("F29",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F31)),"$",""))),ISNUMBER(SEARCH("F30",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F31)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(F31-8029.374999999999)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
+        <f ca="1">IF(COUNT(F30,F31)&lt;2,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F31)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("F30",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F31)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(F31-25)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="H31" s="3" t="str">
-        <v>Add the original base and both separate tax results.</v>
+        <v>Divide the annual excise bill by 12. This is a budgeting amount, not a monthly tax bill.</v>
       </c>
       <c r="I31" s="3" t="str">
         <v>slide 14</v>
@@ -2487,20 +2577,20 @@
         <v>9</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="C32" s="3" t="str">
+        <v>D: assessed value $540,000; F: thousands of assessed value (divide by 1,000).</v>
       </c>
       <c r="D32" s="5"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="5"/>
+      <c r="E32" s="218"/>
+      <c r="F32" s="221"/>
       <c r="G32" s="7" t="str">
-        <f ca="1">IF(COUNT(D32,E32,F32)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F32)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D32",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F32)),"$",""))),ISNUMBER(SEARCH("E32",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F32)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(D32-540000)&lt;=0.01,ABS(E32-0.32)&lt;=0.0000001,ABS(F32-172800)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
+        <f ca="1">IF(COUNT(D32,F32)&lt;2,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F32)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D32",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F32)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(D32-540000)&lt;=0.01,ABS(F32-540)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>40</v>
+      <c r="H32" s="3" t="str">
+        <v>Massachusetts uses the assessor’s full and fair cash value. Divide by 1,000 to match rate units.</v>
       </c>
       <c r="I32" s="3" t="str">
         <v>slide 18</v>
@@ -2511,20 +2601,20 @@
         <v>10</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="103"/>
+        <v>36</v>
+      </c>
+      <c r="C33" s="3" t="str">
+        <v>D: Beverly FY2026 commercial rate $20.98 per $1,000; F: annual property tax using F32.</v>
+      </c>
+      <c r="D33" s="220"/>
+      <c r="E33" s="217"/>
+      <c r="F33" s="223"/>
       <c r="G33" s="7" t="str">
-        <f ca="1">IF(COUNT(D33,E33,F33)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F33)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("D33",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F33)),"$",""))),ISNUMBER(SEARCH("E33",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F33)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(D33-234500)&lt;=0.01,ABS(E33-3450000)&lt;=0.01,ABS(F33-0.068)&lt;=0.0000001),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
+        <f ca="1">IF(COUNT(F32,D33,F33)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F33)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("F32",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F33)),"$",""))),ISNUMBER(SEARCH("D33",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F33)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(D33-20.98)&lt;=0.01,ABS(F33-11329.2)&lt;=0.0000001),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>42</v>
+      <c r="H33" s="3" t="str">
+        <v>Multiply thousands of assessed value F32 by dollars per $1,000 D33.</v>
       </c>
       <c r="I33" s="3" t="str">
         <v>slide 18</v>
@@ -2535,20 +2625,20 @@
         <v>11</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C34" s="3" t="str">
-        <v>F: annual tax due using assessed value F32 and rounded rate F33.</v>
+        <v>F: monthly savings using annual property tax F33.</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="5"/>
       <c r="G34" s="7" t="str">
-        <f ca="1">IF(COUNT(F32,F33,F34)&lt;3,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F34)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("F32",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F34)),"$",""))),ISNUMBER(SEARCH("F33",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F34)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(F34-11750.4)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
+        <f ca="1">IF(COUNT(F33,F34)&lt;2,"Enter inputs and a formula first",IF(NOT(_xlfn.ISFORMULA(F34)),"Use a formula, not a typed answer",IF(NOT(IFERROR(AND(ISNUMBER(SEARCH("F33",SUBSTITUTE(UPPER(_xlfn.FORMULATEXT(F34)),"$","")))),FALSE)),"Use the required input/result references",IF(AND(ABS(F34-944.1)&lt;=0.01),"Correct - explain and test your model","Check the baseline inputs and calculation"))))</f>
         <v>Enter inputs and a formula first</v>
       </c>
       <c r="H34" s="3" t="str">
-        <v>Reference assessed value F32 and rounded rate F33.</v>
+        <v>Divide annual property tax F33 by 12 for monthly savings.</v>
       </c>
       <c r="I34" s="3" t="str">
         <v>slide 18</v>
@@ -2588,7 +2678,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="66" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="66"/>
@@ -2633,8 +2723,8 @@
       <c r="L3" s="67"/>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="68" t="s">
-        <v>44</v>
+      <c r="A4" s="68" t="str">
+        <v>Sales tax and vehicle excise use Massachusetts rules. Property tax uses Beverly FY2026 commercial/residential rates. Example property values are illustrative. Source cells stay unchanged.</v>
       </c>
       <c r="B4" s="68"/>
       <c r="C4" s="68"/>
@@ -2650,7 +2740,7 @@
     </row>
     <row r="5">
       <c r="A5" s="69" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -2661,58 +2751,58 @@
       <c r="H5" s="70"/>
       <c r="I5" s="71"/>
       <c r="J5" s="72" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="K5" s="73"/>
       <c r="L5" s="74"/>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="16" t="str">
+        <v>Amount / original list price / assessed value</v>
+      </c>
+      <c r="E6" s="16" t="str">
+        <v>Discount / vehicle-year percentage</v>
+      </c>
+      <c r="F6" s="16" t="str">
+        <v>Sales rate / dollars per $1,000</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="L6" s="17" t="s">
         <v>48</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D7" s="30">
         <v>1200</v>
@@ -2724,8 +2814,8 @@
         <v>0.0625</v>
       </c>
       <c r="G7" s="39"/>
-      <c r="H7" s="27" t="s">
-        <v>61</v>
+      <c r="H7" s="27" t="str">
+        <v>=ROUND((D7-E7)*F7,2)</v>
       </c>
       <c r="I7" s="30" t="n">
         <f>ROUND((D7-E7)*F7,2)</f>
@@ -2737,13 +2827,13 @@
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="20" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D8" s="31">
         <v>480</v>
@@ -2755,8 +2845,8 @@
         <v>0.0625</v>
       </c>
       <c r="G8" s="40"/>
-      <c r="H8" s="28" t="s">
-        <v>64</v>
+      <c r="H8" s="28" t="str">
+        <v>=ROUND(D8*F8,2)</v>
       </c>
       <c r="I8" s="31" t="n">
         <f>ROUND(D8*F8,2)</f>
@@ -2768,13 +2858,13 @@
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="20" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>28</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D9" s="31">
         <v>78625</v>
@@ -2784,8 +2874,8 @@
         <v>0.0625</v>
       </c>
       <c r="G9" s="40"/>
-      <c r="H9" s="28" t="s">
-        <v>67</v>
+      <c r="H9" s="28" t="str">
+        <v>=ROUND(D9-D9/(1+F9),2)</v>
       </c>
       <c r="I9" s="31" t="n">
         <f>ROUND(D9-D9/(1+F9),2)</f>
@@ -2797,30 +2887,30 @@
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>36</v>
+        <v>55</v>
+      </c>
+      <c r="B10" s="25" t="str">
+        <v>Vehicle excise</v>
       </c>
       <c r="C10" s="25" t="str">
-        <v>Meridian appliance: 6.25% sales and 8% supplied excise tax share a $6,200 base</v>
-      </c>
-      <c r="D10" s="31">
-        <v>6200</v>
-      </c>
-      <c r="E10" s="40"/>
-      <c r="F10" s="177" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="G10" s="40">
-        <v>0.08</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>69</v>
+        <v>Meridian car: original list price $32,000; second year 60%; $25 per $1,000; full year</v>
+      </c>
+      <c r="D10" s="31" t="n">
+        <v>32000</v>
+      </c>
+      <c r="E10" s="198" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F10" s="199" t="n">
+        <v>25</v>
+      </c>
+      <c r="G10" s="40"/>
+      <c r="H10" s="28" t="str">
+        <v>=ROUND(D10*E10*F10/1000,2)</v>
       </c>
       <c r="I10" s="31" t="n">
-        <f>ROUND(D10*(F10+G10),2)</f>
-        <v>883.5</v>
+        <f>ROUND(D10*E10*F10/1000,2)</f>
+        <v>480</v>
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="35"/>
@@ -2828,30 +2918,30 @@
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>36</v>
+        <v>56</v>
+      </c>
+      <c r="B11" s="25" t="str">
+        <v>Vehicle excise</v>
       </c>
       <c r="C11" s="25" t="str">
-        <v>Meridian equipment: 6.25% sales and 9% supplied excise tax share an $8,400 base</v>
-      </c>
-      <c r="D11" s="31">
-        <v>8400</v>
-      </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="177" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="G11" s="40">
-        <v>0.09</v>
-      </c>
-      <c r="H11" s="28" t="s">
-        <v>71</v>
+        <v>Meridian car: original list price $36,000; third year 40%; $25 per $1,000; full year</v>
+      </c>
+      <c r="D11" s="31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E11" s="198" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F11" s="199" t="n">
+        <v>25</v>
+      </c>
+      <c r="G11" s="40"/>
+      <c r="H11" s="28" t="str">
+        <v>=ROUND(D11*F11/1000,2)</v>
       </c>
       <c r="I11" s="31" t="n">
-        <f>ROUND(D11*F11+(D11+D11*F11)*G11,2)</f>
-        <v>1328.25</v>
+        <f>ROUND(D11*F11/1000,2)</f>
+        <v>900</v>
       </c>
       <c r="J11" s="21"/>
       <c r="K11" s="35"/>
@@ -2859,32 +2949,30 @@
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="22" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="32">
+        <v>36</v>
+      </c>
+      <c r="C12" s="26" t="str">
+        <v>Beverly FY2026 commercial office: $820,000 assessed value; commercial $20.98 and residential $10.81 per $1,000</v>
+      </c>
+      <c r="D12" s="32" t="n">
         <v>820000</v>
       </c>
-      <c r="E12" s="41">
-        <v>0.4</v>
-      </c>
-      <c r="F12" s="32">
-        <v>310000</v>
-      </c>
-      <c r="G12" s="32">
-        <v>4750000</v>
-      </c>
-      <c r="H12" s="29" t="s">
-        <v>74</v>
+      <c r="E12" s="41"/>
+      <c r="F12" s="222" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="G12" s="222" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="H12" s="29" t="str">
+        <v>=ROUND(D12/1000*G12,2)</v>
       </c>
       <c r="I12" s="32" t="n">
-        <f>ROUND(D12*ROUND(F12/G12,4),2)</f>
-        <v>53546</v>
+        <f>ROUND(D12/1000*G12,2)</f>
+        <v>8864.2</v>
       </c>
       <c r="J12" s="23"/>
       <c r="K12" s="37"/>
@@ -2920,7 +3008,7 @@
     </row>
     <row r="15">
       <c r="A15" s="75" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B15" s="76"/>
       <c r="C15" s="76"/>
@@ -2936,24 +3024,24 @@
     </row>
     <row r="16">
       <c r="A16" s="82" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B16" s="83"/>
       <c r="C16" s="83"/>
       <c r="D16" s="30" t="n">
         <f>SUM(I7:I12)</f>
-        <v>60476.5</v>
+        <v>14962.95</v>
       </c>
       <c r="E16" s="83" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F16" s="83"/>
       <c r="G16" s="83"/>
       <c r="H16" s="30" t="n">
-        <v>28296.65</v>
+        <v>22757.35</v>
       </c>
       <c r="I16" s="84" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J16" s="84"/>
       <c r="K16" s="34"/>
@@ -2969,7 +3057,7 @@
       <c r="G17" s="42"/>
       <c r="H17" s="42"/>
       <c r="I17" s="85" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="J17" s="85"/>
       <c r="K17" s="36"/>
@@ -2985,7 +3073,7 @@
       <c r="G18" s="42"/>
       <c r="H18" s="42"/>
       <c r="I18" s="85" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="J18" s="85"/>
       <c r="K18" s="36"/>
@@ -3001,7 +3089,7 @@
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
       <c r="I19" s="61" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="J19" s="61"/>
       <c r="K19" s="43"/>
@@ -3023,7 +3111,7 @@
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="62" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B21" s="63"/>
       <c r="C21" s="63"/>
@@ -3117,7 +3205,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="55" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B1" s="56"/>
       <c r="C1" s="56"/>
@@ -3131,170 +3219,170 @@
     </row>
     <row r="3" ht="16">
       <c r="A3" s="4" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" ht="32">
       <c r="A4" s="3" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" ht="32">
       <c r="A5" s="3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" ht="16">
       <c r="A6" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" ht="16">
       <c r="A7" s="3" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" ht="16">
       <c r="A8" s="3" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" ht="32">
-      <c r="A9" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>111</v>
+      <c r="A9" s="3" t="str">
+        <v>Vehicle excise value</v>
+      </c>
+      <c r="B9" s="10" t="str">
+        <v>=ListPrice*YearPercent</v>
+      </c>
+      <c r="C9" s="3" t="str">
+        <v>Uses original manufacturer list price and the vehicle-year percentage.</v>
+      </c>
+      <c r="D9" s="3" t="str">
+        <v>Do not use purchase price or current resale value.</v>
       </c>
     </row>
     <row r="10" ht="32">
-      <c r="A10" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>115</v>
+      <c r="A10" s="3" t="str">
+        <v>Annual vehicle excise</v>
+      </c>
+      <c r="B10" s="10" t="str">
+        <v>=ExciseValue/1000*25</v>
+      </c>
+      <c r="C10" s="3" t="str">
+        <v>Charges $25 for each $1,000 of excise value.</v>
+      </c>
+      <c r="D10" s="3" t="str">
+        <v>Owner pays city/town; these examples assume full-year registration.</v>
       </c>
     </row>
     <row r="11" ht="32">
-      <c r="A11" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>119</v>
+      <c r="A11" s="3" t="str">
+        <v>Thousands of assessed value</v>
+      </c>
+      <c r="B11" s="10" t="str">
+        <v>=AssessedValue/1000</v>
+      </c>
+      <c r="C11" s="3" t="str">
+        <v>Converts the assessor’s value to the units used by the local rate.</v>
+      </c>
+      <c r="D11" s="3" t="str">
+        <v>Do not apply the former 32% or 40% assessment fraction.</v>
       </c>
     </row>
     <row r="12" ht="32">
-      <c r="A12" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>123</v>
+      <c r="A12" s="3" t="str">
+        <v>Annual property tax</v>
+      </c>
+      <c r="B12" s="10" t="str">
+        <v>=ThousandsOfValue*LocalRate</v>
+      </c>
+      <c r="C12" s="3" t="str">
+        <v>Uses the published dollar rate per $1,000.</v>
+      </c>
+      <c r="D12" s="3" t="str">
+        <v>Match municipality, property class, and fiscal year.</v>
       </c>
     </row>
     <row r="13" ht="16">
-      <c r="A13" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>127</v>
+      <c r="A13" s="3" t="str">
+        <v>Direct property-tax formula</v>
+      </c>
+      <c r="B13" s="10" t="str">
+        <v>=AssessedValue/1000*LocalRate</v>
+      </c>
+      <c r="C13" s="3" t="str">
+        <v>Equivalent one-step calculation.</v>
+      </c>
+      <c r="D13" s="3" t="str">
+        <v>The rate is dollars per $1,000, not a percentage.</v>
       </c>
     </row>
     <row r="14" ht="32">
-      <c r="A14" s="3" t="s">
-        <v>128</v>
+      <c r="A14" s="3" t="str">
+        <v>Monthly property-tax savings</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>131</v>
+        <v>92</v>
+      </c>
+      <c r="D14" s="3" t="str">
+        <v>Monthly budgeting amount; actual city billing can differ.</v>
       </c>
     </row>
   </sheetData>
